--- a/data/daily/2026-10/2026-10-18.xlsx
+++ b/data/daily/2026-10/2026-10-18.xlsx
@@ -1195,14 +1195,64 @@
       <row>2</row>
       <rowOff>0</rowOff>
     </from>
+    <ext cx="381000" cy="457200"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="2" name="Image 2" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip cstate="print" r:embed="rId2"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>0</col>
+      <colOff>0</colOff>
+      <row>3</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="381000" cy="457200"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="3" name="Image 3" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip cstate="print" r:embed="rId3"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>0</col>
+      <colOff>0</colOff>
+      <row>4</row>
+      <rowOff>0</rowOff>
+    </from>
     <ext cx="342900" cy="457200"/>
     <pic>
       <nvPicPr>
-        <cNvPr id="2" name="Image 2" descr="Picture"/>
-        <cNvPicPr/>
-      </nvPicPr>
-      <blipFill>
-        <a:blip cstate="print" r:embed="rId2"/>
+        <cNvPr id="4" name="Image 4" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip cstate="print" r:embed="rId4"/>
         <a:stretch>
           <a:fillRect/>
         </a:stretch>
@@ -1217,17 +1267,67 @@
     <from>
       <col>0</col>
       <colOff>0</colOff>
-      <row>3</row>
+      <row>5</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="342900" cy="457200"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="5" name="Image 5" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip cstate="print" r:embed="rId5"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>0</col>
+      <colOff>0</colOff>
+      <row>6</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="342900" cy="457200"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="6" name="Image 6" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip cstate="print" r:embed="rId6"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>0</col>
+      <colOff>0</colOff>
+      <row>7</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="381000" cy="457200"/>
     <pic>
       <nvPicPr>
-        <cNvPr id="3" name="Image 3" descr="Picture"/>
-        <cNvPicPr/>
-      </nvPicPr>
-      <blipFill>
-        <a:blip cstate="print" r:embed="rId3"/>
+        <cNvPr id="7" name="Image 7" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip cstate="print" r:embed="rId7"/>
         <a:stretch>
           <a:fillRect/>
         </a:stretch>
@@ -1242,17 +1342,17 @@
     <from>
       <col>0</col>
       <colOff>0</colOff>
-      <row>4</row>
+      <row>8</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="342900" cy="457200"/>
     <pic>
       <nvPicPr>
-        <cNvPr id="4" name="Image 4" descr="Picture"/>
-        <cNvPicPr/>
-      </nvPicPr>
-      <blipFill>
-        <a:blip cstate="print" r:embed="rId4"/>
+        <cNvPr id="8" name="Image 8" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip cstate="print" r:embed="rId8"/>
         <a:stretch>
           <a:fillRect/>
         </a:stretch>
@@ -1267,110 +1367,10 @@
     <from>
       <col>0</col>
       <colOff>0</colOff>
-      <row>5</row>
-      <rowOff>0</rowOff>
-    </from>
-    <ext cx="381000" cy="457200"/>
-    <pic>
-      <nvPicPr>
-        <cNvPr id="5" name="Image 5" descr="Picture"/>
-        <cNvPicPr/>
-      </nvPicPr>
-      <blipFill>
-        <a:blip cstate="print" r:embed="rId5"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </blipFill>
-      <spPr>
-        <a:prstGeom prst="rect"/>
-      </spPr>
-    </pic>
-    <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>0</col>
-      <colOff>0</colOff>
-      <row>6</row>
-      <rowOff>0</rowOff>
-    </from>
-    <ext cx="381000" cy="457200"/>
-    <pic>
-      <nvPicPr>
-        <cNvPr id="6" name="Image 6" descr="Picture"/>
-        <cNvPicPr/>
-      </nvPicPr>
-      <blipFill>
-        <a:blip cstate="print" r:embed="rId6"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </blipFill>
-      <spPr>
-        <a:prstGeom prst="rect"/>
-      </spPr>
-    </pic>
-    <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>0</col>
-      <colOff>0</colOff>
-      <row>7</row>
-      <rowOff>0</rowOff>
-    </from>
-    <ext cx="342900" cy="457200"/>
-    <pic>
-      <nvPicPr>
-        <cNvPr id="7" name="Image 7" descr="Picture"/>
-        <cNvPicPr/>
-      </nvPicPr>
-      <blipFill>
-        <a:blip cstate="print" r:embed="rId7"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </blipFill>
-      <spPr>
-        <a:prstGeom prst="rect"/>
-      </spPr>
-    </pic>
-    <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>0</col>
-      <colOff>0</colOff>
-      <row>8</row>
-      <rowOff>0</rowOff>
-    </from>
-    <ext cx="381000" cy="457200"/>
-    <pic>
-      <nvPicPr>
-        <cNvPr id="8" name="Image 8" descr="Picture"/>
-        <cNvPicPr/>
-      </nvPicPr>
-      <blipFill>
-        <a:blip cstate="print" r:embed="rId8"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </blipFill>
-      <spPr>
-        <a:prstGeom prst="rect"/>
-      </spPr>
-    </pic>
-    <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>0</col>
-      <colOff>0</colOff>
       <row>9</row>
       <rowOff>0</rowOff>
     </from>
-    <ext cx="381000" cy="457200"/>
+    <ext cx="361950" cy="457200"/>
     <pic>
       <nvPicPr>
         <cNvPr id="9" name="Image 9" descr="Picture"/>
@@ -1450,52 +1450,152 @@
       <row>1</row>
       <rowOff>0</rowOff>
     </from>
+    <ext cx="1028700" cy="1238250"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="2" name="Image 2" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip cstate="print" r:embed="rId2"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>4</col>
+      <colOff>0</colOff>
+      <row>1</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="1028700" cy="1238250"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="3" name="Image 3" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip cstate="print" r:embed="rId3"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>5</col>
+      <colOff>0</colOff>
+      <row>1</row>
+      <rowOff>0</rowOff>
+    </from>
     <ext cx="933450" cy="1238250"/>
     <pic>
       <nvPicPr>
-        <cNvPr id="2" name="Image 2" descr="Picture"/>
-        <cNvPicPr/>
-      </nvPicPr>
-      <blipFill>
-        <a:blip cstate="print" r:embed="rId2"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </blipFill>
-      <spPr>
-        <a:prstGeom prst="rect"/>
-      </spPr>
-    </pic>
-    <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>4</col>
+        <cNvPr id="4" name="Image 4" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip cstate="print" r:embed="rId4"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>6</col>
       <colOff>0</colOff>
       <row>1</row>
       <rowOff>0</rowOff>
     </from>
+    <ext cx="933450" cy="1238250"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="5" name="Image 5" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip cstate="print" r:embed="rId5"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>7</col>
+      <colOff>0</colOff>
+      <row>1</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="933450" cy="1238250"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="6" name="Image 6" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip cstate="print" r:embed="rId6"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>8</col>
+      <colOff>0</colOff>
+      <row>1</row>
+      <rowOff>0</rowOff>
+    </from>
     <ext cx="1028700" cy="1238250"/>
     <pic>
       <nvPicPr>
-        <cNvPr id="3" name="Image 3" descr="Picture"/>
-        <cNvPicPr/>
-      </nvPicPr>
-      <blipFill>
-        <a:blip cstate="print" r:embed="rId3"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </blipFill>
-      <spPr>
-        <a:prstGeom prst="rect"/>
-      </spPr>
-    </pic>
-    <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>5</col>
+        <cNvPr id="7" name="Image 7" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip cstate="print" r:embed="rId7"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>9</col>
       <colOff>0</colOff>
       <row>1</row>
       <rowOff>0</rowOff>
@@ -1503,129 +1603,29 @@
     <ext cx="933450" cy="1238250"/>
     <pic>
       <nvPicPr>
-        <cNvPr id="4" name="Image 4" descr="Picture"/>
-        <cNvPicPr/>
-      </nvPicPr>
-      <blipFill>
-        <a:blip cstate="print" r:embed="rId4"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </blipFill>
-      <spPr>
-        <a:prstGeom prst="rect"/>
-      </spPr>
-    </pic>
-    <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>6</col>
+        <cNvPr id="8" name="Image 8" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip cstate="print" r:embed="rId8"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>10</col>
       <colOff>0</colOff>
       <row>1</row>
       <rowOff>0</rowOff>
     </from>
-    <ext cx="1028700" cy="1238250"/>
-    <pic>
-      <nvPicPr>
-        <cNvPr id="5" name="Image 5" descr="Picture"/>
-        <cNvPicPr/>
-      </nvPicPr>
-      <blipFill>
-        <a:blip cstate="print" r:embed="rId5"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </blipFill>
-      <spPr>
-        <a:prstGeom prst="rect"/>
-      </spPr>
-    </pic>
-    <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>7</col>
-      <colOff>0</colOff>
-      <row>1</row>
-      <rowOff>0</rowOff>
-    </from>
-    <ext cx="1028700" cy="1238250"/>
-    <pic>
-      <nvPicPr>
-        <cNvPr id="6" name="Image 6" descr="Picture"/>
-        <cNvPicPr/>
-      </nvPicPr>
-      <blipFill>
-        <a:blip cstate="print" r:embed="rId6"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </blipFill>
-      <spPr>
-        <a:prstGeom prst="rect"/>
-      </spPr>
-    </pic>
-    <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>8</col>
-      <colOff>0</colOff>
-      <row>1</row>
-      <rowOff>0</rowOff>
-    </from>
-    <ext cx="933450" cy="1238250"/>
-    <pic>
-      <nvPicPr>
-        <cNvPr id="7" name="Image 7" descr="Picture"/>
-        <cNvPicPr/>
-      </nvPicPr>
-      <blipFill>
-        <a:blip cstate="print" r:embed="rId7"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </blipFill>
-      <spPr>
-        <a:prstGeom prst="rect"/>
-      </spPr>
-    </pic>
-    <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>9</col>
-      <colOff>0</colOff>
-      <row>1</row>
-      <rowOff>0</rowOff>
-    </from>
-    <ext cx="1028700" cy="1238250"/>
-    <pic>
-      <nvPicPr>
-        <cNvPr id="8" name="Image 8" descr="Picture"/>
-        <cNvPicPr/>
-      </nvPicPr>
-      <blipFill>
-        <a:blip cstate="print" r:embed="rId8"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </blipFill>
-      <spPr>
-        <a:prstGeom prst="rect"/>
-      </spPr>
-    </pic>
-    <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>10</col>
-      <colOff>0</colOff>
-      <row>1</row>
-      <rowOff>0</rowOff>
-    </from>
-    <ext cx="1028700" cy="1238250"/>
+    <ext cx="990600" cy="1238250"/>
     <pic>
       <nvPicPr>
         <cNvPr id="9" name="Image 9" descr="Picture"/>
@@ -2596,13 +2596,33 @@
         <v>4</v>
       </c>
       <c r="J2" t="n">
-        <v>16301</v>
-      </c>
-      <c r="K2" t="inlineStr"/>
-      <c r="L2" t="inlineStr"/>
-      <c r="M2" t="inlineStr"/>
-      <c r="N2" t="inlineStr"/>
-      <c r="O2" t="inlineStr"/>
+        <v>16302</v>
+      </c>
+      <c r="K2" t="inlineStr">
+        <is>
+          <t>피로 회복 및 활력 증진 — 피로 회복에 효과가 있고 몸이 한결 가벼워짐</t>
+        </is>
+      </c>
+      <c r="L2" t="inlineStr">
+        <is>
+          <t>선물용 고급스러운 포장 — 포장이 고급스러워 선물용으로 매우 좋음</t>
+        </is>
+      </c>
+      <c r="M2" t="inlineStr">
+        <is>
+          <t>편리한 섭취 및 괜찮은 맛 — 먹기 편리하고 액상 맛도 괜찮음</t>
+        </is>
+      </c>
+      <c r="N2" t="inlineStr">
+        <is>
+          <t>배송 지연 발생 — 배송이 엄청 늦게 도착함</t>
+        </is>
+      </c>
+      <c r="O2" t="inlineStr">
+        <is>
+          <t>부담스러운 가격대 — 가격이 다소 비쌈</t>
+        </is>
+      </c>
       <c r="P2" t="inlineStr"/>
     </row>
     <row r="3" ht="38" customHeight="1">
@@ -2643,11 +2663,23 @@
         <v>4</v>
       </c>
       <c r="J3" t="n">
-        <v>15638</v>
-      </c>
-      <c r="K3" t="inlineStr"/>
-      <c r="L3" t="inlineStr"/>
-      <c r="M3" t="inlineStr"/>
+        <v>15640</v>
+      </c>
+      <c r="K3" t="inlineStr">
+        <is>
+          <t>피로 회복 및 건강 증진 — 피로 해소에 도움을 주고 건강해지는 느낌임</t>
+        </is>
+      </c>
+      <c r="L3" t="inlineStr">
+        <is>
+          <t>간편한 섭취 및 휴대성 — 하루치씩 구분되어 휴대 및 간편 섭취 가능함</t>
+        </is>
+      </c>
+      <c r="M3" t="inlineStr">
+        <is>
+          <t>선물용 높은 만족도 — 선물용으로 부담 없고 받는 사람의 만족도가 높음</t>
+        </is>
+      </c>
       <c r="N3" t="inlineStr"/>
       <c r="O3" t="inlineStr"/>
       <c r="P3" t="inlineStr"/>
@@ -2692,9 +2724,21 @@
       <c r="J4" t="n">
         <v>3413</v>
       </c>
-      <c r="K4" t="inlineStr"/>
-      <c r="L4" t="inlineStr"/>
-      <c r="M4" t="inlineStr"/>
+      <c r="K4" t="inlineStr">
+        <is>
+          <t>우수한 피로 회복 효과 — 피로감이 줄고 활기찬 하루를 보내는 데 도움 됨</t>
+        </is>
+      </c>
+      <c r="L4" t="inlineStr">
+        <is>
+          <t>선물하기 좋은 포장과 구성 — 포장이 예쁘고 용량이 넉넉해 선물용으로 적합함</t>
+        </is>
+      </c>
+      <c r="M4" t="inlineStr">
+        <is>
+          <t>편리한 개별 섭취 — 하나씩 간편하게 챙겨 먹기 편리함</t>
+        </is>
+      </c>
       <c r="N4" t="inlineStr"/>
       <c r="O4" t="inlineStr"/>
       <c r="P4" t="inlineStr"/>
@@ -2739,10 +2783,26 @@
       <c r="J5" t="n">
         <v>6525</v>
       </c>
-      <c r="K5" t="inlineStr"/>
-      <c r="L5" t="inlineStr"/>
-      <c r="M5" t="inlineStr"/>
-      <c r="N5" t="inlineStr"/>
+      <c r="K5" t="inlineStr">
+        <is>
+          <t>간편한 젤리 제형 — 물 없이 씹어 먹을 수 있어 섭취가 매우 간편함</t>
+        </is>
+      </c>
+      <c r="L5" t="inlineStr">
+        <is>
+          <t>맛있는 과일 맛 — 거부감 없는 과일 맛 젤리로 맛있게 섭취 가능함</t>
+        </is>
+      </c>
+      <c r="M5" t="inlineStr">
+        <is>
+          <t>안전한 용기 디자인 — 안전캡이 있어 아이가 있는 집에서도 안심됨</t>
+        </is>
+      </c>
+      <c r="N5" t="inlineStr">
+        <is>
+          <t>섭취량 제한의 아쉬움 — 맛있어서 하루 정해진 양만 먹어야 하는 점이 아쉬움</t>
+        </is>
+      </c>
       <c r="O5" t="inlineStr"/>
       <c r="P5" t="inlineStr"/>
     </row>
@@ -2786,11 +2846,31 @@
       <c r="J6" t="n">
         <v>129</v>
       </c>
-      <c r="K6" t="inlineStr"/>
-      <c r="L6" t="inlineStr"/>
-      <c r="M6" t="inlineStr"/>
-      <c r="N6" t="inlineStr"/>
-      <c r="O6" t="inlineStr"/>
+      <c r="K6" t="inlineStr">
+        <is>
+          <t>체력 증진 및 피로 개선 — 피로 회복과 체력 유지에 뛰어난 효과가 있음</t>
+        </is>
+      </c>
+      <c r="L6" t="inlineStr">
+        <is>
+          <t>영양소 올인원 섭취 — 다양한 비타민과 미네랄을 한 번에 챙길 수 있음</t>
+        </is>
+      </c>
+      <c r="M6" t="inlineStr">
+        <is>
+          <t>할인 구매 시 가성비 — 이벤트 할인 시 저렴하게 구매 가능함</t>
+        </is>
+      </c>
+      <c r="N6" t="inlineStr">
+        <is>
+          <t>짧은 유통기한 — 생각보다 유통기한이 짧아서 아쉬움</t>
+        </is>
+      </c>
+      <c r="O6" t="inlineStr">
+        <is>
+          <t>부담스러운 정가 가격 — 평소 가격이 다소 비싸게 느껴짐</t>
+        </is>
+      </c>
       <c r="P6" t="inlineStr"/>
     </row>
     <row r="7" ht="38" customHeight="1">
@@ -2833,9 +2913,21 @@
       <c r="J7" t="n">
         <v>825</v>
       </c>
-      <c r="K7" t="inlineStr"/>
-      <c r="L7" t="inlineStr"/>
-      <c r="M7" t="inlineStr"/>
+      <c r="K7" t="inlineStr">
+        <is>
+          <t>우수한 피로 회복 효과 — 피로 개선 및 환절기 컨디션 관리에 도움 됨</t>
+        </is>
+      </c>
+      <c r="L7" t="inlineStr">
+        <is>
+          <t>간편한 섭취 및 휴대성 — 먹기 편리하고 휴대성이 뛰어남</t>
+        </is>
+      </c>
+      <c r="M7" t="inlineStr">
+        <is>
+          <t>만족스러운 선물 구성 — 구성 및 포장이 우수하여 선물용 만족도가 높음</t>
+        </is>
+      </c>
       <c r="N7" t="inlineStr"/>
       <c r="O7" t="inlineStr"/>
       <c r="P7" t="inlineStr"/>
@@ -2878,13 +2970,33 @@
         <v>4</v>
       </c>
       <c r="J8" t="n">
-        <v>1773</v>
-      </c>
-      <c r="K8" t="inlineStr"/>
-      <c r="L8" t="inlineStr"/>
-      <c r="M8" t="inlineStr"/>
-      <c r="N8" t="inlineStr"/>
-      <c r="O8" t="inlineStr"/>
+        <v>1775</v>
+      </c>
+      <c r="K8" t="inlineStr">
+        <is>
+          <t>활력 충전 및 피로 개선 — 섭취 후 피로가 풀리고 생기가 도는 효과가 있음</t>
+        </is>
+      </c>
+      <c r="L8" t="inlineStr">
+        <is>
+          <t>고급스러운 포장 디자인 — 포장이 고급스러워 선물용으로 매우 만족스러움</t>
+        </is>
+      </c>
+      <c r="M8" t="inlineStr">
+        <is>
+          <t>간편하고 재미있는 섭취 — 버튼을 누르고 섞어 마시는 방식이 편리하고 재미있음</t>
+        </is>
+      </c>
+      <c r="N8" t="inlineStr">
+        <is>
+          <t>분말의 쌉쌀한 맛 — 섞이는 노란 가루에서 쌉쌀한 맛이 느껴짐</t>
+        </is>
+      </c>
+      <c r="O8" t="inlineStr">
+        <is>
+          <t>사용법 숙지 필요 — 버튼을 눌러 가루를 섞는 방식을 미리 숙지해야 함</t>
+        </is>
+      </c>
       <c r="P8" t="inlineStr"/>
     </row>
     <row r="9" ht="38" customHeight="1">
@@ -2908,7 +3020,7 @@
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>28,000원</t>
+          <t>24,900원</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
@@ -2925,12 +3037,28 @@
         <v>4</v>
       </c>
       <c r="J9" t="n">
-        <v>962</v>
-      </c>
-      <c r="K9" t="inlineStr"/>
-      <c r="L9" t="inlineStr"/>
-      <c r="M9" t="inlineStr"/>
-      <c r="N9" t="inlineStr"/>
+        <v>963</v>
+      </c>
+      <c r="K9" t="inlineStr">
+        <is>
+          <t>면역력 강화 및 피로 개선 — 감기 예방 및 입병 완화, 피로 해소에 도움 됨</t>
+        </is>
+      </c>
+      <c r="L9" t="inlineStr">
+        <is>
+          <t>합리적인 할인 가격 — 행사 할인을 통해 가성비 높게 구매함</t>
+        </is>
+      </c>
+      <c r="M9" t="inlineStr">
+        <is>
+          <t>새로운 가루형 제형 — 분말 형태로 섭취하는 방식이 색다름</t>
+        </is>
+      </c>
+      <c r="N9" t="inlineStr">
+        <is>
+          <t>강한 신맛과 쓴맛 — 신맛과 쓴맛이 강해 섭취 시 부담스러울 수 있음</t>
+        </is>
+      </c>
       <c r="O9" t="inlineStr"/>
       <c r="P9" t="inlineStr"/>
     </row>
@@ -2965,18 +3093,30 @@
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>https://st.kakaocdn.net/product/gift/product/20261016132819_da2df5cea93d47b1813674e6bfee72d8.jpg</t>
+          <t>https://st.kakaocdn.net/product/gift/product/20261018111100_823e5a0bdcf24c7e938d9ca85b824be9.jpeg</t>
         </is>
       </c>
       <c r="I10" t="n">
         <v>4</v>
       </c>
       <c r="J10" t="n">
-        <v>529</v>
-      </c>
-      <c r="K10" t="inlineStr"/>
-      <c r="L10" t="inlineStr"/>
-      <c r="M10" t="inlineStr"/>
+        <v>532</v>
+      </c>
+      <c r="K10" t="inlineStr">
+        <is>
+          <t>높은 가성비 및 할인 — 할인 행사로 저렴하게 구매하여 가성비가 훌륭함</t>
+        </is>
+      </c>
+      <c r="L10" t="inlineStr">
+        <is>
+          <t>풍성한 추가 사은품 — 아임비타 등 증정품 구성에 대한 만족도가 높음</t>
+        </is>
+      </c>
+      <c r="M10" t="inlineStr">
+        <is>
+          <t>신속한 배송 — 배송이 매우 빠르고 정확함</t>
+        </is>
+      </c>
       <c r="N10" t="inlineStr"/>
       <c r="O10" t="inlineStr"/>
       <c r="P10" t="inlineStr"/>
@@ -3021,9 +3161,21 @@
       <c r="J11" t="n">
         <v>839</v>
       </c>
-      <c r="K11" t="inlineStr"/>
-      <c r="L11" t="inlineStr"/>
-      <c r="M11" t="inlineStr"/>
+      <c r="K11" t="inlineStr">
+        <is>
+          <t>피로 회복 및 활력 증진 — 피로 해소와 체력 영양 보충에 매우 효과적임</t>
+        </is>
+      </c>
+      <c r="L11" t="inlineStr">
+        <is>
+          <t>위생적인 이중 제형 — 액상과 정제가 구분되어 편리하고 위생적으로 섭취 가능함</t>
+        </is>
+      </c>
+      <c r="M11" t="inlineStr">
+        <is>
+          <t>휴대 및 섭취 간편성 — 외출 시 들고 다니며 간편하게 먹기 좋음</t>
+        </is>
+      </c>
       <c r="N11" t="inlineStr"/>
       <c r="O11" t="inlineStr"/>
       <c r="P11" t="inlineStr"/>
@@ -3068,10 +3220,26 @@
       <c r="J12" t="n">
         <v>1743</v>
       </c>
-      <c r="K12" t="inlineStr"/>
-      <c r="L12" t="inlineStr"/>
-      <c r="M12" t="inlineStr"/>
-      <c r="N12" t="inlineStr"/>
+      <c r="K12" t="inlineStr">
+        <is>
+          <t>소화 및 배변 활동 개선 — 속 더부룩함 완화 및 화장실 이용이 원활해짐</t>
+        </is>
+      </c>
+      <c r="L12" t="inlineStr">
+        <is>
+          <t>고소하고 우수한 맛 — 맛이 고소하여 아이부터 어른까지 맛있게 먹음</t>
+        </is>
+      </c>
+      <c r="M12" t="inlineStr">
+        <is>
+          <t>풍성한 사은품과 포장 — 선물용 상자가 고급스럽고 사은품 혜택이 다양함</t>
+        </is>
+      </c>
+      <c r="N12" t="inlineStr">
+        <is>
+          <t>기프티콘 사은품 누락 — 증정하기로 한 기프티콘이 지급되지 않음</t>
+        </is>
+      </c>
       <c r="O12" t="inlineStr"/>
       <c r="P12" t="inlineStr"/>
     </row>
@@ -3115,10 +3283,26 @@
       <c r="J13" t="n">
         <v>935</v>
       </c>
-      <c r="K13" t="inlineStr"/>
-      <c r="L13" t="inlineStr"/>
-      <c r="M13" t="inlineStr"/>
-      <c r="N13" t="inlineStr"/>
+      <c r="K13" t="inlineStr">
+        <is>
+          <t>소화 증진 및 변비 개선 — 소화가 잘되고 가스 차는 증상 및 변비 개선에 효과적임</t>
+        </is>
+      </c>
+      <c r="L13" t="inlineStr">
+        <is>
+          <t>맛있는 섭취감 — 맛이 좋아 거부감 없이 편하게 섭취 가능함</t>
+        </is>
+      </c>
+      <c r="M13" t="inlineStr">
+        <is>
+          <t>저렴한 가격과 증정 혜택 — 할인된 가격에 다양한 증정품이 포함되어 만족스럽음</t>
+        </is>
+      </c>
+      <c r="N13" t="inlineStr">
+        <is>
+          <t>교환 및 환불 불가 정책 — 구매 후 교환이나 환불이 되지 않아 불편함</t>
+        </is>
+      </c>
       <c r="O13" t="inlineStr"/>
       <c r="P13" t="inlineStr"/>
     </row>
@@ -3143,7 +3327,7 @@
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>45,500원</t>
+          <t>45,900원</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
@@ -3162,12 +3346,36 @@
       <c r="J14" t="n">
         <v>155</v>
       </c>
-      <c r="K14" t="inlineStr"/>
-      <c r="L14" t="inlineStr"/>
-      <c r="M14" t="inlineStr"/>
-      <c r="N14" t="inlineStr"/>
-      <c r="O14" t="inlineStr"/>
-      <c r="P14" t="inlineStr"/>
+      <c r="K14" t="inlineStr">
+        <is>
+          <t>높은 포만감과 맛 — 다양하고 맛있는 양념으로 든든한 포만감을 줌</t>
+        </is>
+      </c>
+      <c r="L14" t="inlineStr">
+        <is>
+          <t>가성비 및 이벤트 혜택 — 할인 행사로 합리적인 가격에 구매할 수 있음</t>
+        </is>
+      </c>
+      <c r="M14" t="inlineStr">
+        <is>
+          <t>만족스러운 사은품 가방 — 보냉백 사은품 디자인이 예쁘고 배송이 빠름</t>
+        </is>
+      </c>
+      <c r="N14" t="inlineStr">
+        <is>
+          <t>다소 강한 양념 간 — 생각보다 양념 간이 세게 느껴짐</t>
+        </is>
+      </c>
+      <c r="O14" t="inlineStr">
+        <is>
+          <t>배송 및 오배송 문제 — 주문한 구성과 다르게 제품이 중복되어 배송됨</t>
+        </is>
+      </c>
+      <c r="P14" t="inlineStr">
+        <is>
+          <t>포장 불량 및 소스 누출 — 진공 포장이 헐렁하거나 제품이 터져 소스가 묻어옴</t>
+        </is>
+      </c>
     </row>
     <row r="15" ht="38" customHeight="1">
       <c r="B15" t="inlineStr">
@@ -3209,9 +3417,21 @@
       <c r="J15" t="n">
         <v>266</v>
       </c>
-      <c r="K15" t="inlineStr"/>
-      <c r="L15" t="inlineStr"/>
-      <c r="M15" t="inlineStr"/>
+      <c r="K15" t="inlineStr">
+        <is>
+          <t>맛있고 간편한 섭취 — 맛이 뛰어나 출출할 때 간식용으로 먹기 좋음</t>
+        </is>
+      </c>
+      <c r="L15" t="inlineStr">
+        <is>
+          <t>풍성한 고품질 사은품 — 포토카드 및 단백질바 등 증정품 퀄리티가 우수함</t>
+        </is>
+      </c>
+      <c r="M15" t="inlineStr">
+        <is>
+          <t>빠르고 깔끔한 배송 — 포장이 깔끔하게 오고 배송이 신속함</t>
+        </is>
+      </c>
       <c r="N15" t="inlineStr"/>
       <c r="O15" t="inlineStr"/>
       <c r="P15" t="inlineStr"/>
@@ -3256,9 +3476,21 @@
       <c r="J16" t="n">
         <v>69</v>
       </c>
-      <c r="K16" t="inlineStr"/>
-      <c r="L16" t="inlineStr"/>
-      <c r="M16" t="inlineStr"/>
+      <c r="K16" t="inlineStr">
+        <is>
+          <t>촉촉하고 맛있는 식감 — 닭가슴살이 퍽퍽하지 않고 촉촉하며 맛이 뛰어남</t>
+        </is>
+      </c>
+      <c r="L16" t="inlineStr">
+        <is>
+          <t>다양한 구성의 식단 관리 — 다양한 맛으로 구성되어 질리지 않고 식단 관리가 가능함</t>
+        </is>
+      </c>
+      <c r="M16" t="inlineStr">
+        <is>
+          <t>간편한 전자레인지 조리 — 전자레인지로 데워 바로 먹을 수 있어 편리함</t>
+        </is>
+      </c>
       <c r="N16" t="inlineStr"/>
       <c r="O16" t="inlineStr"/>
       <c r="P16" t="inlineStr"/>
@@ -3303,10 +3535,26 @@
       <c r="J17" t="n">
         <v>756</v>
       </c>
-      <c r="K17" t="inlineStr"/>
-      <c r="L17" t="inlineStr"/>
-      <c r="M17" t="inlineStr"/>
-      <c r="N17" t="inlineStr"/>
+      <c r="K17" t="inlineStr">
+        <is>
+          <t>고급스러운 선물 포장 — 포장 패키지가 매우 고급스럽고 예뻐 선물용으로 최적임</t>
+        </is>
+      </c>
+      <c r="L17" t="inlineStr">
+        <is>
+          <t>맛있는 섭취감 — 맛이 좋아 거부감 없이 즐겁게 마실 수 있음</t>
+        </is>
+      </c>
+      <c r="M17" t="inlineStr">
+        <is>
+          <t>피로 해소 및 피부 건강 — 피로감이 덜하고 피부 탄력 개선 효과가 기대됨</t>
+        </is>
+      </c>
+      <c r="N17" t="inlineStr">
+        <is>
+          <t>부담스러운 정가 가격 — 가격이 다소 비싸 할인 기간에만 구매하게 됨</t>
+        </is>
+      </c>
       <c r="O17" t="inlineStr"/>
       <c r="P17" t="inlineStr"/>
     </row>
@@ -3348,11 +3596,23 @@
         <v>4</v>
       </c>
       <c r="J18" t="n">
-        <v>73</v>
-      </c>
-      <c r="K18" t="inlineStr"/>
-      <c r="L18" t="inlineStr"/>
-      <c r="M18" t="inlineStr"/>
+        <v>74</v>
+      </c>
+      <c r="K18" t="inlineStr">
+        <is>
+          <t>확실한 숙취 해소 효과 — 다음 날 속이 덜 부대끼고 깔끔하게 숙취가 해소됨</t>
+        </is>
+      </c>
+      <c r="L18" t="inlineStr">
+        <is>
+          <t>휴대 및 섭취 간편성 — 스틱형 포장으로 모임이나 회식 시 휴대하고 먹기 편함</t>
+        </is>
+      </c>
+      <c r="M18" t="inlineStr">
+        <is>
+          <t>깔끔한 선물용 포장 — 선물 세트 포장과 종이가방 구성이 깔끔함</t>
+        </is>
+      </c>
       <c r="N18" t="inlineStr"/>
       <c r="O18" t="inlineStr"/>
       <c r="P18" t="inlineStr"/>
@@ -3397,10 +3657,26 @@
       <c r="J19" t="n">
         <v>30</v>
       </c>
-      <c r="K19" t="inlineStr"/>
-      <c r="L19" t="inlineStr"/>
-      <c r="M19" t="inlineStr"/>
-      <c r="N19" t="inlineStr"/>
+      <c r="K19" t="inlineStr">
+        <is>
+          <t>속 편한 락토프리 — 락토프리 제품으로 섭취 후 속이 편안함</t>
+        </is>
+      </c>
+      <c r="L19" t="inlineStr">
+        <is>
+          <t>비린 맛 없는 뛰어난 맛 — 단백질 특유의 비린 맛이 없고 맛이 우수함</t>
+        </is>
+      </c>
+      <c r="M19" t="inlineStr">
+        <is>
+          <t>신속한 배송 및 증정품 — 배송이 빠르고 추가 증정 상품 구성에 만족함</t>
+        </is>
+      </c>
+      <c r="N19" t="inlineStr">
+        <is>
+          <t>특정 맛의 느끼함 — 밀크바나나 맛 등 특정 맛은 다소 느끼하게 느껴짐</t>
+        </is>
+      </c>
       <c r="O19" t="inlineStr"/>
       <c r="P19" t="inlineStr"/>
     </row>
@@ -3444,9 +3720,21 @@
       <c r="J20" t="n">
         <v>10</v>
       </c>
-      <c r="K20" t="inlineStr"/>
-      <c r="L20" t="inlineStr"/>
-      <c r="M20" t="inlineStr"/>
+      <c r="K20" t="inlineStr">
+        <is>
+          <t>뛰어난 맛과 적은 텁텁함 — 일반 음료처럼 매우 맛있고 단백질 특유의 텁텁함이 적음</t>
+        </is>
+      </c>
+      <c r="L20" t="inlineStr">
+        <is>
+          <t>풍성한 토핑과 포만감 — 크런치볼 토핑이 많아 씹는 식감이 좋고 포만감이 오래 유지됨</t>
+        </is>
+      </c>
+      <c r="M20" t="inlineStr">
+        <is>
+          <t>물만 넣어도 간편한 섭취 — 물만 타서 흔들어 먹어도 달콤하고 맛이 우수함</t>
+        </is>
+      </c>
       <c r="N20" t="inlineStr"/>
       <c r="O20" t="inlineStr"/>
       <c r="P20" t="inlineStr"/>
@@ -3491,9 +3779,21 @@
       <c r="J21" t="n">
         <v>218</v>
       </c>
-      <c r="K21" t="inlineStr"/>
-      <c r="L21" t="inlineStr"/>
-      <c r="M21" t="inlineStr"/>
+      <c r="K21" t="inlineStr">
+        <is>
+          <t>비린 맛 없는 깔끔한 맛 — 단백질 특유의 비리거나 텁텁한 맛없이 일반 음료처럼 맛있음</t>
+        </is>
+      </c>
+      <c r="L21" t="inlineStr">
+        <is>
+          <t>든든한 포만감 제공 — 섭취 후 은근히 배가 차서 출출할 때 간식으로 좋음</t>
+        </is>
+      </c>
+      <c r="M21" t="inlineStr">
+        <is>
+          <t>빠른 배송 및 선물 적합성 — 배송이 빠르고 지인이나 부모님 선물용으로 만족스러움</t>
+        </is>
+      </c>
       <c r="N21" t="inlineStr"/>
       <c r="O21" t="inlineStr"/>
       <c r="P21" t="inlineStr"/>
@@ -3816,10 +4116,10 @@
         </is>
       </c>
       <c r="C7" s="3" t="n">
-        <v>16301</v>
+        <v>16302</v>
       </c>
       <c r="D7" s="3" t="n">
-        <v>15638</v>
+        <v>15640</v>
       </c>
       <c r="E7" s="3" t="n">
         <v>3413</v>
@@ -3834,49 +4134,132 @@
         <v>825</v>
       </c>
       <c r="I7" s="3" t="n">
-        <v>1773</v>
+        <v>1775</v>
       </c>
       <c r="J7" s="3" t="n">
-        <v>962</v>
+        <v>963</v>
       </c>
       <c r="K7" s="3" t="n">
-        <v>529</v>
+        <v>532</v>
       </c>
       <c r="L7" s="3" t="n">
         <v>839</v>
       </c>
     </row>
-    <row r="8">
+    <row r="8" ht="90" customHeight="1">
       <c r="B8" s="1" t="inlineStr">
         <is>
           <t>긍정리뷰</t>
         </is>
       </c>
-      <c r="C8" s="3" t="inlineStr"/>
-      <c r="D8" s="3" t="inlineStr"/>
-      <c r="E8" s="3" t="inlineStr"/>
-      <c r="F8" s="3" t="inlineStr"/>
-      <c r="G8" s="3" t="inlineStr"/>
-      <c r="H8" s="3" t="inlineStr"/>
-      <c r="I8" s="3" t="inlineStr"/>
-      <c r="J8" s="3" t="inlineStr"/>
-      <c r="K8" s="3" t="inlineStr"/>
-      <c r="L8" s="3" t="inlineStr"/>
-    </row>
-    <row r="9">
+      <c r="C8" s="3" t="inlineStr">
+        <is>
+          <t>피로 회복 및 활력 증진 — 피로 회복에 효과가 있고 몸이 한결 가벼워짐
+선물용 고급스러운 포장 — 포장이 고급스러워 선물용으로 매우 좋음
+편리한 섭취 및 괜찮은 맛 — 먹기 편리하고 액상 맛도 괜찮음</t>
+        </is>
+      </c>
+      <c r="D8" s="3" t="inlineStr">
+        <is>
+          <t>피로 회복 및 건강 증진 — 피로 해소에 도움을 주고 건강해지는 느낌임
+간편한 섭취 및 휴대성 — 하루치씩 구분되어 휴대 및 간편 섭취 가능함
+선물용 높은 만족도 — 선물용으로 부담 없고 받는 사람의 만족도가 높음</t>
+        </is>
+      </c>
+      <c r="E8" s="3" t="inlineStr">
+        <is>
+          <t>우수한 피로 회복 효과 — 피로감이 줄고 활기찬 하루를 보내는 데 도움 됨
+선물하기 좋은 포장과 구성 — 포장이 예쁘고 용량이 넉넉해 선물용으로 적합함
+편리한 개별 섭취 — 하나씩 간편하게 챙겨 먹기 편리함</t>
+        </is>
+      </c>
+      <c r="F8" s="3" t="inlineStr">
+        <is>
+          <t>간편한 젤리 제형 — 물 없이 씹어 먹을 수 있어 섭취가 매우 간편함
+맛있는 과일 맛 — 거부감 없는 과일 맛 젤리로 맛있게 섭취 가능함
+안전한 용기 디자인 — 안전캡이 있어 아이가 있는 집에서도 안심됨</t>
+        </is>
+      </c>
+      <c r="G8" s="3" t="inlineStr">
+        <is>
+          <t>체력 증진 및 피로 개선 — 피로 회복과 체력 유지에 뛰어난 효과가 있음
+영양소 올인원 섭취 — 다양한 비타민과 미네랄을 한 번에 챙길 수 있음
+할인 구매 시 가성비 — 이벤트 할인 시 저렴하게 구매 가능함</t>
+        </is>
+      </c>
+      <c r="H8" s="3" t="inlineStr">
+        <is>
+          <t>우수한 피로 회복 효과 — 피로 개선 및 환절기 컨디션 관리에 도움 됨
+간편한 섭취 및 휴대성 — 먹기 편리하고 휴대성이 뛰어남
+만족스러운 선물 구성 — 구성 및 포장이 우수하여 선물용 만족도가 높음</t>
+        </is>
+      </c>
+      <c r="I8" s="3" t="inlineStr">
+        <is>
+          <t>활력 충전 및 피로 개선 — 섭취 후 피로가 풀리고 생기가 도는 효과가 있음
+고급스러운 포장 디자인 — 포장이 고급스러워 선물용으로 매우 만족스러움
+간편하고 재미있는 섭취 — 버튼을 누르고 섞어 마시는 방식이 편리하고 재미있음</t>
+        </is>
+      </c>
+      <c r="J8" s="3" t="inlineStr">
+        <is>
+          <t>면역력 강화 및 피로 개선 — 감기 예방 및 입병 완화, 피로 해소에 도움 됨
+합리적인 할인 가격 — 행사 할인을 통해 가성비 높게 구매함
+새로운 가루형 제형 — 분말 형태로 섭취하는 방식이 색다름</t>
+        </is>
+      </c>
+      <c r="K8" s="3" t="inlineStr">
+        <is>
+          <t>높은 가성비 및 할인 — 할인 행사로 저렴하게 구매하여 가성비가 훌륭함
+풍성한 추가 사은품 — 아임비타 등 증정품 구성에 대한 만족도가 높음
+신속한 배송 — 배송이 매우 빠르고 정확함</t>
+        </is>
+      </c>
+      <c r="L8" s="3" t="inlineStr">
+        <is>
+          <t>피로 회복 및 활력 증진 — 피로 해소와 체력 영양 보충에 매우 효과적임
+위생적인 이중 제형 — 액상과 정제가 구분되어 편리하고 위생적으로 섭취 가능함
+휴대 및 섭취 간편성 — 외출 시 들고 다니며 간편하게 먹기 좋음</t>
+        </is>
+      </c>
+    </row>
+    <row r="9" ht="60" customHeight="1">
       <c r="B9" s="1" t="inlineStr">
         <is>
           <t>부정리뷰</t>
         </is>
       </c>
-      <c r="C9" s="3" t="inlineStr"/>
+      <c r="C9" s="3" t="inlineStr">
+        <is>
+          <t>배송 지연 발생 — 배송이 엄청 늦게 도착함
+부담스러운 가격대 — 가격이 다소 비쌈</t>
+        </is>
+      </c>
       <c r="D9" s="3" t="inlineStr"/>
       <c r="E9" s="3" t="inlineStr"/>
-      <c r="F9" s="3" t="inlineStr"/>
-      <c r="G9" s="3" t="inlineStr"/>
+      <c r="F9" s="3" t="inlineStr">
+        <is>
+          <t>섭취량 제한의 아쉬움 — 맛있어서 하루 정해진 양만 먹어야 하는 점이 아쉬움</t>
+        </is>
+      </c>
+      <c r="G9" s="3" t="inlineStr">
+        <is>
+          <t>짧은 유통기한 — 생각보다 유통기한이 짧아서 아쉬움
+부담스러운 정가 가격 — 평소 가격이 다소 비싸게 느껴짐</t>
+        </is>
+      </c>
       <c r="H9" s="3" t="inlineStr"/>
-      <c r="I9" s="3" t="inlineStr"/>
-      <c r="J9" s="3" t="inlineStr"/>
+      <c r="I9" s="3" t="inlineStr">
+        <is>
+          <t>분말의 쌉쌀한 맛 — 섞이는 노란 가루에서 쌉쌀한 맛이 느껴짐
+사용법 숙지 필요 — 버튼을 눌러 가루를 섞는 방식을 미리 숙지해야 함</t>
+        </is>
+      </c>
+      <c r="J9" s="3" t="inlineStr">
+        <is>
+          <t>강한 신맛과 쓴맛 — 신맛과 쓴맛이 강해 섭취 시 부담스러울 수 있음</t>
+        </is>
+      </c>
       <c r="K9" s="3" t="inlineStr"/>
       <c r="L9" s="3" t="inlineStr"/>
     </row>
@@ -3923,7 +4306,7 @@
       </c>
       <c r="J10" s="3" t="inlineStr">
         <is>
-          <t>28,000원</t>
+          <t>24,900원</t>
         </is>
       </c>
       <c r="K10" s="3" t="inlineStr">
@@ -4301,7 +4684,7 @@
         <v>756</v>
       </c>
       <c r="I19" s="3" t="n">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="J19" s="3" t="n">
         <v>30</v>
@@ -4313,37 +4696,119 @@
         <v>218</v>
       </c>
     </row>
-    <row r="20">
+    <row r="20" ht="90" customHeight="1">
       <c r="B20" s="1" t="inlineStr">
         <is>
           <t>긍정리뷰</t>
         </is>
       </c>
-      <c r="C20" s="3" t="inlineStr"/>
-      <c r="D20" s="3" t="inlineStr"/>
-      <c r="E20" s="3" t="inlineStr"/>
-      <c r="F20" s="3" t="inlineStr"/>
-      <c r="G20" s="3" t="inlineStr"/>
-      <c r="H20" s="3" t="inlineStr"/>
-      <c r="I20" s="3" t="inlineStr"/>
-      <c r="J20" s="3" t="inlineStr"/>
-      <c r="K20" s="3" t="inlineStr"/>
-      <c r="L20" s="3" t="inlineStr"/>
-    </row>
-    <row r="21">
+      <c r="C20" s="3" t="inlineStr">
+        <is>
+          <t>소화 및 배변 활동 개선 — 속 더부룩함 완화 및 화장실 이용이 원활해짐
+고소하고 우수한 맛 — 맛이 고소하여 아이부터 어른까지 맛있게 먹음
+풍성한 사은품과 포장 — 선물용 상자가 고급스럽고 사은품 혜택이 다양함</t>
+        </is>
+      </c>
+      <c r="D20" s="3" t="inlineStr">
+        <is>
+          <t>소화 증진 및 변비 개선 — 소화가 잘되고 가스 차는 증상 및 변비 개선에 효과적임
+맛있는 섭취감 — 맛이 좋아 거부감 없이 편하게 섭취 가능함
+저렴한 가격과 증정 혜택 — 할인된 가격에 다양한 증정품이 포함되어 만족스럽음</t>
+        </is>
+      </c>
+      <c r="E20" s="3" t="inlineStr">
+        <is>
+          <t>높은 포만감과 맛 — 다양하고 맛있는 양념으로 든든한 포만감을 줌
+가성비 및 이벤트 혜택 — 할인 행사로 합리적인 가격에 구매할 수 있음
+만족스러운 사은품 가방 — 보냉백 사은품 디자인이 예쁘고 배송이 빠름</t>
+        </is>
+      </c>
+      <c r="F20" s="3" t="inlineStr">
+        <is>
+          <t>맛있고 간편한 섭취 — 맛이 뛰어나 출출할 때 간식용으로 먹기 좋음
+풍성한 고품질 사은품 — 포토카드 및 단백질바 등 증정품 퀄리티가 우수함
+빠르고 깔끔한 배송 — 포장이 깔끔하게 오고 배송이 신속함</t>
+        </is>
+      </c>
+      <c r="G20" s="3" t="inlineStr">
+        <is>
+          <t>촉촉하고 맛있는 식감 — 닭가슴살이 퍽퍽하지 않고 촉촉하며 맛이 뛰어남
+다양한 구성의 식단 관리 — 다양한 맛으로 구성되어 질리지 않고 식단 관리가 가능함
+간편한 전자레인지 조리 — 전자레인지로 데워 바로 먹을 수 있어 편리함</t>
+        </is>
+      </c>
+      <c r="H20" s="3" t="inlineStr">
+        <is>
+          <t>고급스러운 선물 포장 — 포장 패키지가 매우 고급스럽고 예뻐 선물용으로 최적임
+맛있는 섭취감 — 맛이 좋아 거부감 없이 즐겁게 마실 수 있음
+피로 해소 및 피부 건강 — 피로감이 덜하고 피부 탄력 개선 효과가 기대됨</t>
+        </is>
+      </c>
+      <c r="I20" s="3" t="inlineStr">
+        <is>
+          <t>확실한 숙취 해소 효과 — 다음 날 속이 덜 부대끼고 깔끔하게 숙취가 해소됨
+휴대 및 섭취 간편성 — 스틱형 포장으로 모임이나 회식 시 휴대하고 먹기 편함
+깔끔한 선물용 포장 — 선물 세트 포장과 종이가방 구성이 깔끔함</t>
+        </is>
+      </c>
+      <c r="J20" s="3" t="inlineStr">
+        <is>
+          <t>속 편한 락토프리 — 락토프리 제품으로 섭취 후 속이 편안함
+비린 맛 없는 뛰어난 맛 — 단백질 특유의 비린 맛이 없고 맛이 우수함
+신속한 배송 및 증정품 — 배송이 빠르고 추가 증정 상품 구성에 만족함</t>
+        </is>
+      </c>
+      <c r="K20" s="3" t="inlineStr">
+        <is>
+          <t>뛰어난 맛과 적은 텁텁함 — 일반 음료처럼 매우 맛있고 단백질 특유의 텁텁함이 적음
+풍성한 토핑과 포만감 — 크런치볼 토핑이 많아 씹는 식감이 좋고 포만감이 오래 유지됨
+물만 넣어도 간편한 섭취 — 물만 타서 흔들어 먹어도 달콤하고 맛이 우수함</t>
+        </is>
+      </c>
+      <c r="L20" s="3" t="inlineStr">
+        <is>
+          <t>비린 맛 없는 깔끔한 맛 — 단백질 특유의 비리거나 텁텁한 맛없이 일반 음료처럼 맛있음
+든든한 포만감 제공 — 섭취 후 은근히 배가 차서 출출할 때 간식으로 좋음
+빠른 배송 및 선물 적합성 — 배송이 빠르고 지인이나 부모님 선물용으로 만족스러움</t>
+        </is>
+      </c>
+    </row>
+    <row r="21" ht="90" customHeight="1">
       <c r="B21" s="1" t="inlineStr">
         <is>
           <t>부정리뷰</t>
         </is>
       </c>
-      <c r="C21" s="3" t="inlineStr"/>
-      <c r="D21" s="3" t="inlineStr"/>
-      <c r="E21" s="3" t="inlineStr"/>
+      <c r="C21" s="3" t="inlineStr">
+        <is>
+          <t>기프티콘 사은품 누락 — 증정하기로 한 기프티콘이 지급되지 않음</t>
+        </is>
+      </c>
+      <c r="D21" s="3" t="inlineStr">
+        <is>
+          <t>교환 및 환불 불가 정책 — 구매 후 교환이나 환불이 되지 않아 불편함</t>
+        </is>
+      </c>
+      <c r="E21" s="3" t="inlineStr">
+        <is>
+          <t>다소 강한 양념 간 — 생각보다 양념 간이 세게 느껴짐
+배송 및 오배송 문제 — 주문한 구성과 다르게 제품이 중복되어 배송됨
+포장 불량 및 소스 누출 — 진공 포장이 헐렁하거나 제품이 터져 소스가 묻어옴</t>
+        </is>
+      </c>
       <c r="F21" s="3" t="inlineStr"/>
       <c r="G21" s="3" t="inlineStr"/>
-      <c r="H21" s="3" t="inlineStr"/>
+      <c r="H21" s="3" t="inlineStr">
+        <is>
+          <t>부담스러운 정가 가격 — 가격이 다소 비싸 할인 기간에만 구매하게 됨</t>
+        </is>
+      </c>
       <c r="I21" s="3" t="inlineStr"/>
-      <c r="J21" s="3" t="inlineStr"/>
+      <c r="J21" s="3" t="inlineStr">
+        <is>
+          <t>특정 맛의 느끼함 — 밀크바나나 맛 등 특정 맛은 다소 느끼하게 느껴짐</t>
+        </is>
+      </c>
       <c r="K21" s="3" t="inlineStr"/>
       <c r="L21" s="3" t="inlineStr"/>
     </row>
@@ -4365,7 +4830,7 @@
       </c>
       <c r="E22" s="3" t="inlineStr">
         <is>
-          <t>45,500원</t>
+          <t>45,900원</t>
         </is>
       </c>
       <c r="F22" s="3" t="inlineStr">
@@ -4590,7 +5055,7 @@
     <row r="2" ht="38" customHeight="1">
       <c r="B2" t="inlineStr">
         <is>
-          <t>다이어트/체중관리</t>
+          <t>기타/특수목적</t>
         </is>
       </c>
       <c r="C2" t="n">
@@ -4598,12 +5063,12 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>[우형재 PICK] 익스트림 모노크레아틴 플러스 120 g 40일분</t>
+          <t>닥터블릿 푸응 7days 팻버닝 21캡슐</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>익스트림</t>
+          <t>닥터블릿</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
@@ -4613,31 +5078,47 @@
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>https://www.daisomall.co.kr/pd/pdr/SCR_PDR_0001?pdNo=987253276&amp;recmYn=N</t>
+          <t>https://www.daisomall.co.kr/pd/pdr/SCR_PDR_0001?pdNo=613602085&amp;recmYn=N</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>https://cdn.daisomall.co.kr/file/PD/20260422/qm625V7JKEa8Iu7GrFAf987253276_00_01qm625V7JKEa8Iu7GrFAf.jpg</t>
+          <t>https://cdn.daisomall.co.kr/file/PD/20260624/m6tznB24o1VYvw4vwVs3613602085_00_00m6tznB24o1VYvw4vwVs3.jpg</t>
         </is>
       </c>
       <c r="I2" t="n">
-        <v>4.8</v>
+        <v>4.7</v>
       </c>
       <c r="J2" t="n">
-        <v>841</v>
-      </c>
-      <c r="K2" t="inlineStr"/>
-      <c r="L2" t="inlineStr"/>
+        <v>2884</v>
+      </c>
+      <c r="K2" t="inlineStr">
+        <is>
+          <t>심리적 안도감 제공 — 꾸준히 먹으면 안 먹는 것보다 낫다는 안도감을 줌</t>
+        </is>
+      </c>
+      <c r="L2" t="inlineStr">
+        <is>
+          <t>신속한 배송 — 배송이 빠르고 안전하게 도착함</t>
+        </is>
+      </c>
       <c r="M2" t="inlineStr"/>
-      <c r="N2" t="inlineStr"/>
-      <c r="O2" t="inlineStr"/>
+      <c r="N2" t="inlineStr">
+        <is>
+          <t>섭취 후 피로감 유발 — 먹고 나면 잠이 오고 피곤한 느낌이 듦</t>
+        </is>
+      </c>
+      <c r="O2" t="inlineStr">
+        <is>
+          <t>체감 효과의 부족 — 다이어트 체중 감량 효과가 크게 느껴지지 않음</t>
+        </is>
+      </c>
       <c r="P2" t="inlineStr"/>
     </row>
     <row r="3" ht="38" customHeight="1">
       <c r="B3" t="inlineStr">
         <is>
-          <t>마그네슘</t>
+          <t>비타민D</t>
         </is>
       </c>
       <c r="C3" t="n">
@@ -4645,38 +5126,50 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>자연관 리프레쉬 마그네슘＆L-테아닌 4병 4일분</t>
+          <t>대웅제약 비타민D 4000IU 10정 10일분</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>자연관</t>
+          <t>대웅제약</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>5,000원</t>
+          <t>1,000원</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>https://www.daisomall.co.kr/pd/pdr/SCR_PDR_0001?pdNo=032627142&amp;recmYn=N</t>
+          <t>https://www.daisomall.co.kr/pd/pdr/SCR_PDR_0001?pdNo=600000281&amp;recmYn=N</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>https://cdn.daisomall.co.kr/file/PD/20260612/IiBr1SI0rlUycwbkaeGq032627142_00_01IiBr1SI0rlUycwbkaeGq.jpg</t>
+          <t>https://cdn.daisomall.co.kr/file/PD/20260504/H44oDYbaAQPekxvnTd9T600000281_00_01H44oDYbaAQPekxvnTd9T.png</t>
         </is>
       </c>
       <c r="I3" t="n">
         <v>4.8</v>
       </c>
       <c r="J3" t="n">
-        <v>335</v>
-      </c>
-      <c r="K3" t="inlineStr"/>
-      <c r="L3" t="inlineStr"/>
-      <c r="M3" t="inlineStr"/>
+        <v>355</v>
+      </c>
+      <c r="K3" t="inlineStr">
+        <is>
+          <t>뛰어난 가성비 — 소포장 구성 대비 가격과 용량이 합리적임</t>
+        </is>
+      </c>
+      <c r="L3" t="inlineStr">
+        <is>
+          <t>구매 접근성 및 편의성 — 다이소에서 저렴하고 손쉽게 구입할 수 있음</t>
+        </is>
+      </c>
+      <c r="M3" t="inlineStr">
+        <is>
+          <t>효율적인 고함량 구성 — 함량이 높아 효율적인 비타민D 보충이 가능함</t>
+        </is>
+      </c>
       <c r="N3" t="inlineStr"/>
       <c r="O3" t="inlineStr"/>
       <c r="P3" t="inlineStr"/>
@@ -4684,7 +5177,7 @@
     <row r="4" ht="38" customHeight="1">
       <c r="B4" t="inlineStr">
         <is>
-          <t>기타/특수목적</t>
+          <t>혈행</t>
         </is>
       </c>
       <c r="C4" t="n">
@@ -4692,12 +5185,12 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>동국제약 마데카 리포좀 레티놀C 20포</t>
+          <t>대웅제약 코엔자임 Q10 30캡슐 30일분</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>동국제약</t>
+          <t>대웅제약</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
@@ -4707,23 +5200,35 @@
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>https://www.daisomall.co.kr/pd/pdr/SCR_PDR_0001?pdNo=610910601&amp;recmYn=N</t>
+          <t>https://www.daisomall.co.kr/pd/pdr/SCR_PDR_0001?pdNo=600000144&amp;recmYn=N</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>https://cdn.daisomall.co.kr/file/PD/20250502/YBmj8aPscGIkmB6O6RuJ610910601_00_00YBmj8aPscGIkmB6O6RuJ.jpg</t>
+          <t>https://cdn.daisomall.co.kr/file/PD/20250408/OqDM0kpIHoqFD3okk28W600000144_00_00OqDM0kpIHoqFD3okk28W.png</t>
         </is>
       </c>
       <c r="I4" t="n">
         <v>4.8</v>
       </c>
       <c r="J4" t="n">
-        <v>665</v>
-      </c>
-      <c r="K4" t="inlineStr"/>
-      <c r="L4" t="inlineStr"/>
-      <c r="M4" t="inlineStr"/>
+        <v>7411</v>
+      </c>
+      <c r="K4" t="inlineStr">
+        <is>
+          <t>명확한 건강 체감 효과 — 섭취 시 건강 관리와 혈행 개선 효과가 확실히 느껴짐</t>
+        </is>
+      </c>
+      <c r="L4" t="inlineStr">
+        <is>
+          <t>합리적인 가격과 재구매 — 다이소에서 파는 가성비 영양제로 재구매율이 높음</t>
+        </is>
+      </c>
+      <c r="M4" t="inlineStr">
+        <is>
+          <t>빠른 배송 서비스 — 배송이 신속하게 이루어짐</t>
+        </is>
+      </c>
       <c r="N4" t="inlineStr"/>
       <c r="O4" t="inlineStr"/>
       <c r="P4" t="inlineStr"/>
@@ -4731,7 +5236,7 @@
     <row r="5" ht="38" customHeight="1">
       <c r="B5" t="inlineStr">
         <is>
-          <t>다이어트/체중관리</t>
+          <t>기타/특수목적</t>
         </is>
       </c>
       <c r="C5" t="n">
@@ -4739,46 +5244,62 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>종근당 데일리와이즈 혈당컷 다이어트 12정 12일분</t>
+          <t>자연관 정성담은 배도라지스틱 12포</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>종근당</t>
+          <t>자연관</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>2,000원</t>
+          <t>5,000원</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>https://www.daisomall.co.kr/pd/pdr/SCR_PDR_0001?pdNo=032306201&amp;recmYn=N</t>
+          <t>https://www.daisomall.co.kr/pd/pdr/SCR_PDR_0001?pdNo=901762093&amp;recmYn=N</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>https://cdn.daisomall.co.kr/file/PD/20260406/NBw0phjtTvR7tEfBicGr032306201_00_01NBw0phjtTvR7tEfBicGr.jpg</t>
+          <t>https://cdn.daisomall.co.kr/file/PD/20260508/SdledEzpIdjdFFQW6W8g901762093_00_00SdledEzpIdjdFFQW6W8g.png</t>
         </is>
       </c>
       <c r="I5" t="n">
         <v>4.7</v>
       </c>
       <c r="J5" t="n">
-        <v>1515</v>
-      </c>
-      <c r="K5" t="inlineStr"/>
-      <c r="L5" t="inlineStr"/>
-      <c r="M5" t="inlineStr"/>
-      <c r="N5" t="inlineStr"/>
+        <v>977</v>
+      </c>
+      <c r="K5" t="inlineStr">
+        <is>
+          <t>뛰어난 맛과 식감 — 매우 맛있어서 부담 없이 섭취 가능함</t>
+        </is>
+      </c>
+      <c r="L5" t="inlineStr">
+        <is>
+          <t>기관지 관리 및 기침 완화 — 헛기침이 나올 때 먹으면 목이 완화되는 데 도움 됨</t>
+        </is>
+      </c>
+      <c r="M5" t="inlineStr">
+        <is>
+          <t>다양한 섭취 방법 — 그냥 먹거나 물에 타서 차로 마실 수 있어 간편함</t>
+        </is>
+      </c>
+      <c r="N5" t="inlineStr">
+        <is>
+          <t>미미한 효과 체감 — 체감되는 효과가 뚜렷하지는 않음</t>
+        </is>
+      </c>
       <c r="O5" t="inlineStr"/>
       <c r="P5" t="inlineStr"/>
     </row>
     <row r="6" ht="38" customHeight="1">
       <c r="B6" t="inlineStr">
         <is>
-          <t>기타/특수목적</t>
+          <t>비타민D</t>
         </is>
       </c>
       <c r="C6" t="n">
@@ -4786,12 +5307,12 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>대웅제약 밀크씨슬 30정 30일분</t>
+          <t>오브맘 비타민D＆아연 하루구미 30일분</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>대웅제약</t>
+          <t>오브맘</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
@@ -4801,31 +5322,47 @@
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>https://www.daisomall.co.kr/pd/pdr/SCR_PDR_0001?pdNo=600000134&amp;recmYn=N</t>
+          <t>https://www.daisomall.co.kr/pd/pdr/SCR_PDR_0001?pdNo=613602130&amp;recmYn=N</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>https://cdn.daisomall.co.kr/file/PD/20250408/bzKNvkJzwy2KdAqrXtDQ600000134_00_00bzKNvkJzwy2KdAqrXtDQ.png</t>
+          <t>https://cdn.daisomall.co.kr/file/PD/20250922/dxtu28UFPhWKbi5IG3n8613602130_00_01dxtu28UFPhWKbi5IG3n8.jpg</t>
         </is>
       </c>
       <c r="I6" t="n">
         <v>4.8</v>
       </c>
       <c r="J6" t="n">
-        <v>4112</v>
-      </c>
-      <c r="K6" t="inlineStr"/>
-      <c r="L6" t="inlineStr"/>
-      <c r="M6" t="inlineStr"/>
-      <c r="N6" t="inlineStr"/>
+        <v>1701</v>
+      </c>
+      <c r="K6" t="inlineStr">
+        <is>
+          <t>맛있는 자몽맛 젤리 — 새콤달콤한 자몽 맛 젤리로 맛있게 섭취 가능함</t>
+        </is>
+      </c>
+      <c r="L6" t="inlineStr">
+        <is>
+          <t>간편한 지속 섭취 — 알약 부담 없이 간식처럼 꾸준히 챙겨 먹기 좋음</t>
+        </is>
+      </c>
+      <c r="M6" t="inlineStr">
+        <is>
+          <t>만족스러운 비타민 보충 — 꾸준히 먹었을 때 비타민 보충 체감 효과가 있음</t>
+        </is>
+      </c>
+      <c r="N6" t="inlineStr">
+        <is>
+          <t>아쉬운 제품 끝맛 — 첫맛은 매우 맛있으나 끝맛이 살짝 아쉬움</t>
+        </is>
+      </c>
       <c r="O6" t="inlineStr"/>
       <c r="P6" t="inlineStr"/>
     </row>
     <row r="7" ht="38" customHeight="1">
       <c r="B7" t="inlineStr">
         <is>
-          <t>마그네슘</t>
+          <t>루테인/눈건강</t>
         </is>
       </c>
       <c r="C7" t="n">
@@ -4833,39 +5370,51 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>대웅제약 마그네슘 30정 30일분</t>
+          <t>종근당건강 눈건강엔 루테인지아잔틴</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>대웅제약</t>
+          <t>종근당건강</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>3,000원</t>
+          <t>5,000원</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>https://www.daisomall.co.kr/pd/pdr/SCR_PDR_0001?pdNo=600000128&amp;recmYn=N</t>
+          <t>https://www.daisomall.co.kr/pd/pdr/SCR_PDR_0001?pdNo=591580541&amp;recmYn=N</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>https://cdn.daisomall.co.kr/file/PD/20250408/DZz3h5SxY2J2FqaEB9qZ600000128_00_00DZz3h5SxY2J2FqaEB9qZ.png</t>
+          <t>https://cdn.daisomall.co.kr/file/PD/20250430/yuK2zGjcuX8RmMDP9k9P591580541_00_00yuK2zGjcuX8RmMDP9k9P.jpg</t>
         </is>
       </c>
       <c r="I7" t="n">
         <v>4.8</v>
       </c>
       <c r="J7" t="n">
-        <v>6953</v>
-      </c>
-      <c r="K7" t="inlineStr"/>
-      <c r="L7" t="inlineStr"/>
+        <v>1854</v>
+      </c>
+      <c r="K7" t="inlineStr">
+        <is>
+          <t>적당한 알약 크기 — 알약 크기가 적당하여 목넘김이 편함</t>
+        </is>
+      </c>
+      <c r="L7" t="inlineStr">
+        <is>
+          <t>지속적인 눈 건강 관리 — 눈 건강을 위해 부담 없이 꾸준히 먹기 좋음</t>
+        </is>
+      </c>
       <c r="M7" t="inlineStr"/>
-      <c r="N7" t="inlineStr"/>
+      <c r="N7" t="inlineStr">
+        <is>
+          <t>뚜렷한 효과 미체감 — 꾸준히 먹고 있으나 즉각적인 효과 체감은 명확하지 않음</t>
+        </is>
+      </c>
       <c r="O7" t="inlineStr"/>
       <c r="P7" t="inlineStr"/>
     </row>
@@ -4880,38 +5429,50 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>종근당 데일리와이즈 글루타치온 PDRN 구미 7일분</t>
+          <t>동화 부채표 배도라지쌍화 5포 5일분</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>종근당</t>
+          <t>동화약품</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>1,000원</t>
+          <t>2,000원</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>https://www.daisomall.co.kr/pd/pdr/SCR_PDR_0001?pdNo=032306205&amp;recmYn=N</t>
+          <t>https://www.daisomall.co.kr/pd/pdr/SCR_PDR_0001?pdNo=601618637&amp;recmYn=N</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>https://cdn.daisomall.co.kr/file/PD/20260417/3ZIc8SM52diH1RyBcU9M032306205_00_013ZIc8SM52diH1RyBcU9M.jpg</t>
+          <t>https://cdn.daisomall.co.kr/file/PD/20260406/xHnNEgPvPnLilc6RIN7P601618637_00_00xHnNEgPvPnLilc6RIN7P.jpg</t>
         </is>
       </c>
       <c r="I8" t="n">
         <v>4.7</v>
       </c>
       <c r="J8" t="n">
-        <v>764</v>
-      </c>
-      <c r="K8" t="inlineStr"/>
-      <c r="L8" t="inlineStr"/>
-      <c r="M8" t="inlineStr"/>
+        <v>478</v>
+      </c>
+      <c r="K8" t="inlineStr">
+        <is>
+          <t>초기 감기 완화 및 피로 회복 — 으슬으슬할 때나 피로할 때 먹기 좋고 감기 기운을 완화해 줌</t>
+        </is>
+      </c>
+      <c r="L8" t="inlineStr">
+        <is>
+          <t>진하고 맛있는 쌍화탕 — 다양한 한약재가 들어가 진하고 우수한 맛을 냄</t>
+        </is>
+      </c>
+      <c r="M8" t="inlineStr">
+        <is>
+          <t>합리적인 가격과 빠른 배송 — 가격이 저렴하고 배송이 빠름</t>
+        </is>
+      </c>
       <c r="N8" t="inlineStr"/>
       <c r="O8" t="inlineStr"/>
       <c r="P8" t="inlineStr"/>
@@ -4919,7 +5480,7 @@
     <row r="9" ht="38" customHeight="1">
       <c r="B9" t="inlineStr">
         <is>
-          <t>루테인/눈건강</t>
+          <t>기타/특수목적</t>
         </is>
       </c>
       <c r="C9" t="n">
@@ -4927,46 +5488,62 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>안국약품 토비콤 루테인 지아잔틴 24캡슐</t>
+          <t>[옥수수수염＆호박] 동국제약 맛있는 센텔라 공주캔디 20정 20일분</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>안국약품</t>
+          <t>동국제약</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>5,000원</t>
+          <t>3,000원</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>https://www.daisomall.co.kr/pd/pdr/SCR_PDR_0001?pdNo=611982830&amp;recmYn=N</t>
+          <t>https://www.daisomall.co.kr/pd/pdr/SCR_PDR_0001?pdNo=610911213&amp;recmYn=N</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>https://cdn.daisomall.co.kr/file/PD/20250623/xCRETYTkHbPblUcjT18I611982830_00_00xCRETYTkHbPblUcjT18I.jpg</t>
+          <t>https://cdn.daisomall.co.kr/file/PD/20260907/E3CpURjLLswf9MgzRChF610911213_00_01E3CpURjLLswf9MgzRChF.jpg</t>
         </is>
       </c>
       <c r="I9" t="n">
-        <v>4.8</v>
+        <v>4.6</v>
       </c>
       <c r="J9" t="n">
-        <v>1184</v>
-      </c>
-      <c r="K9" t="inlineStr"/>
-      <c r="L9" t="inlineStr"/>
-      <c r="M9" t="inlineStr"/>
-      <c r="N9" t="inlineStr"/>
+        <v>181</v>
+      </c>
+      <c r="K9" t="inlineStr">
+        <is>
+          <t>맛있는 간식 형태 — 맛이 좋아 식사 후나 입이 심심할 때 간식처럼 먹기 좋음</t>
+        </is>
+      </c>
+      <c r="L9" t="inlineStr">
+        <is>
+          <t>씹어 먹기 편한 식감 — 오독오독 씹어 먹기 좋아서 섭취가 간편함</t>
+        </is>
+      </c>
+      <c r="M9" t="inlineStr">
+        <is>
+          <t>가벼운 몸 상태 체감 — 섭취 후 몸이 한결 가벼워지는 느낌을 받음</t>
+        </is>
+      </c>
+      <c r="N9" t="inlineStr">
+        <is>
+          <t>이상한 맛과 식감 — 맛이 없고 씹을 때 질감이나 식감이 거부감을 줄 수 있음</t>
+        </is>
+      </c>
       <c r="O9" t="inlineStr"/>
       <c r="P9" t="inlineStr"/>
     </row>
     <row r="10" ht="38" customHeight="1">
       <c r="B10" t="inlineStr">
         <is>
-          <t>비타민D</t>
+          <t>다이어트/체중관리</t>
         </is>
       </c>
       <c r="C10" t="n">
@@ -4974,38 +5551,50 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>대웅제약 비타민D 4000IU 10정 10일분</t>
+          <t>락피도 티니핑 쾌변스틱 12포 12일분</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>대웅제약</t>
+          <t>락피도</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>1,000원</t>
+          <t>5,000원</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>https://www.daisomall.co.kr/pd/pdr/SCR_PDR_0001?pdNo=600000281&amp;recmYn=N</t>
+          <t>https://www.daisomall.co.kr/pd/pdr/SCR_PDR_0001?pdNo=951817121&amp;recmYn=N</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>https://cdn.daisomall.co.kr/file/PD/20260504/H44oDYbaAQPekxvnTd9T600000281_00_01H44oDYbaAQPekxvnTd9T.png</t>
+          <t>https://cdn.daisomall.co.kr/file/PD/20260226/d2rmOd3RsE864TxS1ei6951817121_00_01d2rmOd3RsE864TxS1ei6.jpg</t>
         </is>
       </c>
       <c r="I10" t="n">
         <v>4.8</v>
       </c>
       <c r="J10" t="n">
-        <v>355</v>
-      </c>
-      <c r="K10" t="inlineStr"/>
-      <c r="L10" t="inlineStr"/>
-      <c r="M10" t="inlineStr"/>
+        <v>427</v>
+      </c>
+      <c r="K10" t="inlineStr">
+        <is>
+          <t>복통 없는 확실한 배변 — 배가 아프거나 불편함 없이 화장실을 잘 가도록 도와줌</t>
+        </is>
+      </c>
+      <c r="L10" t="inlineStr">
+        <is>
+          <t>위생적인 개별 스틱 포장 — 한 포씩 개별 포장되어 챙겨 먹기 편함</t>
+        </is>
+      </c>
+      <c r="M10" t="inlineStr">
+        <is>
+          <t>부담 없는 저렴한 가격 — 가격이 저렴하여 자주 구매하기 좋음</t>
+        </is>
+      </c>
       <c r="N10" t="inlineStr"/>
       <c r="O10" t="inlineStr"/>
       <c r="P10" t="inlineStr"/>
@@ -5021,7 +5610,7 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>대웅제약 콘드로이친 30정 30일분</t>
+          <t>대웅제약 녹차카테킨 30정 30일분</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
@@ -5036,24 +5625,36 @@
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>https://www.daisomall.co.kr/pd/pdr/SCR_PDR_0001?pdNo=600000152&amp;recmYn=N</t>
+          <t>https://www.daisomall.co.kr/pd/pdr/SCR_PDR_0001?pdNo=600000136&amp;recmYn=N</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>https://cdn.daisomall.co.kr/file/PD/20250408/b7btdcjQN0UwyzjBmHvY600000152_00_00b7btdcjQN0UwyzjBmHvY.png</t>
+          <t>https://cdn.daisomall.co.kr/file/PD/20250408/5KgtE2Z5pfS6P1gIBIIh600000136_00_005KgtE2Z5pfS6P1gIBIIh.png</t>
         </is>
       </c>
       <c r="I11" t="n">
         <v>4.8</v>
       </c>
       <c r="J11" t="n">
-        <v>1296</v>
-      </c>
-      <c r="K11" t="inlineStr"/>
-      <c r="L11" t="inlineStr"/>
+        <v>3957</v>
+      </c>
+      <c r="K11" t="inlineStr">
+        <is>
+          <t>뛰어난 가성비 — 가격 부담이 적어 지속 구매하기에 가성비가 훌륭함</t>
+        </is>
+      </c>
+      <c r="L11" t="inlineStr">
+        <is>
+          <t>체중 유지 도움 — 더 이상 체중이 증가하지 않도록 유지하는 데 도움 됨</t>
+        </is>
+      </c>
       <c r="M11" t="inlineStr"/>
-      <c r="N11" t="inlineStr"/>
+      <c r="N11" t="inlineStr">
+        <is>
+          <t>체중 감량 효과 미흡 — 약 복용만으로는 직접적인 체중 감량 효과가 크지 않음</t>
+        </is>
+      </c>
       <c r="O11" t="inlineStr"/>
       <c r="P11" t="inlineStr"/>
     </row>
@@ -5168,47 +5769,47 @@
       </c>
       <c r="C3" s="3" t="inlineStr">
         <is>
+          <t>기타/특수목적</t>
+        </is>
+      </c>
+      <c r="D3" s="3" t="inlineStr">
+        <is>
+          <t>비타민D</t>
+        </is>
+      </c>
+      <c r="E3" s="3" t="inlineStr">
+        <is>
+          <t>혈행</t>
+        </is>
+      </c>
+      <c r="F3" s="3" t="inlineStr">
+        <is>
+          <t>기타/특수목적</t>
+        </is>
+      </c>
+      <c r="G3" s="3" t="inlineStr">
+        <is>
+          <t>비타민D</t>
+        </is>
+      </c>
+      <c r="H3" s="3" t="inlineStr">
+        <is>
+          <t>루테인/눈건강</t>
+        </is>
+      </c>
+      <c r="I3" s="3" t="inlineStr">
+        <is>
+          <t>기타/특수목적</t>
+        </is>
+      </c>
+      <c r="J3" s="3" t="inlineStr">
+        <is>
+          <t>기타/특수목적</t>
+        </is>
+      </c>
+      <c r="K3" s="3" t="inlineStr">
+        <is>
           <t>다이어트/체중관리</t>
-        </is>
-      </c>
-      <c r="D3" s="3" t="inlineStr">
-        <is>
-          <t>마그네슘</t>
-        </is>
-      </c>
-      <c r="E3" s="3" t="inlineStr">
-        <is>
-          <t>기타/특수목적</t>
-        </is>
-      </c>
-      <c r="F3" s="3" t="inlineStr">
-        <is>
-          <t>다이어트/체중관리</t>
-        </is>
-      </c>
-      <c r="G3" s="3" t="inlineStr">
-        <is>
-          <t>기타/특수목적</t>
-        </is>
-      </c>
-      <c r="H3" s="3" t="inlineStr">
-        <is>
-          <t>마그네슘</t>
-        </is>
-      </c>
-      <c r="I3" s="3" t="inlineStr">
-        <is>
-          <t>기타/특수목적</t>
-        </is>
-      </c>
-      <c r="J3" s="3" t="inlineStr">
-        <is>
-          <t>루테인/눈건강</t>
-        </is>
-      </c>
-      <c r="K3" s="3" t="inlineStr">
-        <is>
-          <t>비타민D</t>
         </is>
       </c>
       <c r="L3" s="3" t="inlineStr">
@@ -5225,47 +5826,47 @@
       </c>
       <c r="C4" s="3" t="inlineStr">
         <is>
-          <t>익스트림</t>
+          <t>닥터블릿</t>
         </is>
       </c>
       <c r="D4" s="3" t="inlineStr">
         <is>
+          <t>대웅제약</t>
+        </is>
+      </c>
+      <c r="E4" s="3" t="inlineStr">
+        <is>
+          <t>대웅제약</t>
+        </is>
+      </c>
+      <c r="F4" s="3" t="inlineStr">
+        <is>
           <t>자연관</t>
         </is>
       </c>
-      <c r="E4" s="3" t="inlineStr">
+      <c r="G4" s="3" t="inlineStr">
+        <is>
+          <t>오브맘</t>
+        </is>
+      </c>
+      <c r="H4" s="3" t="inlineStr">
+        <is>
+          <t>종근당건강</t>
+        </is>
+      </c>
+      <c r="I4" s="3" t="inlineStr">
+        <is>
+          <t>동화약품</t>
+        </is>
+      </c>
+      <c r="J4" s="3" t="inlineStr">
         <is>
           <t>동국제약</t>
         </is>
       </c>
-      <c r="F4" s="3" t="inlineStr">
-        <is>
-          <t>종근당</t>
-        </is>
-      </c>
-      <c r="G4" s="3" t="inlineStr">
-        <is>
-          <t>대웅제약</t>
-        </is>
-      </c>
-      <c r="H4" s="3" t="inlineStr">
-        <is>
-          <t>대웅제약</t>
-        </is>
-      </c>
-      <c r="I4" s="3" t="inlineStr">
-        <is>
-          <t>종근당</t>
-        </is>
-      </c>
-      <c r="J4" s="3" t="inlineStr">
-        <is>
-          <t>안국약품</t>
-        </is>
-      </c>
       <c r="K4" s="3" t="inlineStr">
         <is>
-          <t>대웅제약</t>
+          <t>락피도</t>
         </is>
       </c>
       <c r="L4" s="3" t="inlineStr">
@@ -5282,52 +5883,52 @@
       </c>
       <c r="C5" s="3" t="inlineStr">
         <is>
-          <t>[우형재 PICK] 익스트림 모노크레아틴 플러스 120 g 40일분</t>
+          <t>닥터블릿 푸응 7days 팻버닝 21캡슐</t>
         </is>
       </c>
       <c r="D5" s="3" t="inlineStr">
         <is>
-          <t>자연관 리프레쉬 마그네슘＆L-테아닌 4병 4일분</t>
+          <t>대웅제약 비타민D 4000IU 10정 10일분</t>
         </is>
       </c>
       <c r="E5" s="3" t="inlineStr">
         <is>
-          <t>동국제약 마데카 리포좀 레티놀C 20포</t>
+          <t>대웅제약 코엔자임 Q10 30캡슐 30일분</t>
         </is>
       </c>
       <c r="F5" s="3" t="inlineStr">
         <is>
-          <t>종근당 데일리와이즈 혈당컷 다이어트 12정 12일분</t>
+          <t>자연관 정성담은 배도라지스틱 12포</t>
         </is>
       </c>
       <c r="G5" s="3" t="inlineStr">
         <is>
-          <t>대웅제약 밀크씨슬 30정 30일분</t>
+          <t>오브맘 비타민D＆아연 하루구미 30일분</t>
         </is>
       </c>
       <c r="H5" s="3" t="inlineStr">
         <is>
-          <t>대웅제약 마그네슘 30정 30일분</t>
+          <t>종근당건강 눈건강엔 루테인지아잔틴</t>
         </is>
       </c>
       <c r="I5" s="3" t="inlineStr">
         <is>
-          <t>종근당 데일리와이즈 글루타치온 PDRN 구미 7일분</t>
+          <t>동화 부채표 배도라지쌍화 5포 5일분</t>
         </is>
       </c>
       <c r="J5" s="3" t="inlineStr">
         <is>
-          <t>안국약품 토비콤 루테인 지아잔틴 24캡슐</t>
+          <t>[옥수수수염＆호박] 동국제약 맛있는 센텔라 공주캔디 20정 20일분</t>
         </is>
       </c>
       <c r="K5" s="3" t="inlineStr">
         <is>
-          <t>대웅제약 비타민D 4000IU 10정 10일분</t>
+          <t>락피도 티니핑 쾌변스틱 12포 12일분</t>
         </is>
       </c>
       <c r="L5" s="3" t="inlineStr">
         <is>
-          <t>대웅제약 콘드로이친 30정 30일분</t>
+          <t>대웅제약 녹차카테킨 30정 30일분</t>
         </is>
       </c>
     </row>
@@ -5338,7 +5939,7 @@
         </is>
       </c>
       <c r="C6" s="3" t="n">
-        <v>4.8</v>
+        <v>4.7</v>
       </c>
       <c r="D6" s="3" t="n">
         <v>4.8</v>
@@ -5359,7 +5960,7 @@
         <v>4.7</v>
       </c>
       <c r="J6" s="3" t="n">
-        <v>4.8</v>
+        <v>4.6</v>
       </c>
       <c r="K6" s="3" t="n">
         <v>4.8</v>
@@ -5375,69 +5976,151 @@
         </is>
       </c>
       <c r="C7" s="3" t="n">
-        <v>841</v>
+        <v>2884</v>
       </c>
       <c r="D7" s="3" t="n">
-        <v>335</v>
+        <v>355</v>
       </c>
       <c r="E7" s="3" t="n">
-        <v>665</v>
+        <v>7411</v>
       </c>
       <c r="F7" s="3" t="n">
-        <v>1515</v>
+        <v>977</v>
       </c>
       <c r="G7" s="3" t="n">
-        <v>4112</v>
+        <v>1701</v>
       </c>
       <c r="H7" s="3" t="n">
-        <v>6953</v>
+        <v>1854</v>
       </c>
       <c r="I7" s="3" t="n">
-        <v>764</v>
+        <v>478</v>
       </c>
       <c r="J7" s="3" t="n">
-        <v>1184</v>
+        <v>181</v>
       </c>
       <c r="K7" s="3" t="n">
-        <v>355</v>
+        <v>427</v>
       </c>
       <c r="L7" s="3" t="n">
-        <v>1296</v>
-      </c>
-    </row>
-    <row r="8">
+        <v>3957</v>
+      </c>
+    </row>
+    <row r="8" ht="90" customHeight="1">
       <c r="B8" s="1" t="inlineStr">
         <is>
           <t>긍정리뷰</t>
         </is>
       </c>
-      <c r="C8" s="3" t="inlineStr"/>
-      <c r="D8" s="3" t="inlineStr"/>
-      <c r="E8" s="3" t="inlineStr"/>
-      <c r="F8" s="3" t="inlineStr"/>
-      <c r="G8" s="3" t="inlineStr"/>
-      <c r="H8" s="3" t="inlineStr"/>
-      <c r="I8" s="3" t="inlineStr"/>
-      <c r="J8" s="3" t="inlineStr"/>
-      <c r="K8" s="3" t="inlineStr"/>
-      <c r="L8" s="3" t="inlineStr"/>
-    </row>
-    <row r="9">
+      <c r="C8" s="3" t="inlineStr">
+        <is>
+          <t>심리적 안도감 제공 — 꾸준히 먹으면 안 먹는 것보다 낫다는 안도감을 줌
+신속한 배송 — 배송이 빠르고 안전하게 도착함</t>
+        </is>
+      </c>
+      <c r="D8" s="3" t="inlineStr">
+        <is>
+          <t>뛰어난 가성비 — 소포장 구성 대비 가격과 용량이 합리적임
+구매 접근성 및 편의성 — 다이소에서 저렴하고 손쉽게 구입할 수 있음
+효율적인 고함량 구성 — 함량이 높아 효율적인 비타민D 보충이 가능함</t>
+        </is>
+      </c>
+      <c r="E8" s="3" t="inlineStr">
+        <is>
+          <t>명확한 건강 체감 효과 — 섭취 시 건강 관리와 혈행 개선 효과가 확실히 느껴짐
+합리적인 가격과 재구매 — 다이소에서 파는 가성비 영양제로 재구매율이 높음
+빠른 배송 서비스 — 배송이 신속하게 이루어짐</t>
+        </is>
+      </c>
+      <c r="F8" s="3" t="inlineStr">
+        <is>
+          <t>뛰어난 맛과 식감 — 매우 맛있어서 부담 없이 섭취 가능함
+기관지 관리 및 기침 완화 — 헛기침이 나올 때 먹으면 목이 완화되는 데 도움 됨
+다양한 섭취 방법 — 그냥 먹거나 물에 타서 차로 마실 수 있어 간편함</t>
+        </is>
+      </c>
+      <c r="G8" s="3" t="inlineStr">
+        <is>
+          <t>맛있는 자몽맛 젤리 — 새콤달콤한 자몽 맛 젤리로 맛있게 섭취 가능함
+간편한 지속 섭취 — 알약 부담 없이 간식처럼 꾸준히 챙겨 먹기 좋음
+만족스러운 비타민 보충 — 꾸준히 먹었을 때 비타민 보충 체감 효과가 있음</t>
+        </is>
+      </c>
+      <c r="H8" s="3" t="inlineStr">
+        <is>
+          <t>적당한 알약 크기 — 알약 크기가 적당하여 목넘김이 편함
+지속적인 눈 건강 관리 — 눈 건강을 위해 부담 없이 꾸준히 먹기 좋음</t>
+        </is>
+      </c>
+      <c r="I8" s="3" t="inlineStr">
+        <is>
+          <t>초기 감기 완화 및 피로 회복 — 으슬으슬할 때나 피로할 때 먹기 좋고 감기 기운을 완화해 줌
+진하고 맛있는 쌍화탕 — 다양한 한약재가 들어가 진하고 우수한 맛을 냄
+합리적인 가격과 빠른 배송 — 가격이 저렴하고 배송이 빠름</t>
+        </is>
+      </c>
+      <c r="J8" s="3" t="inlineStr">
+        <is>
+          <t>맛있는 간식 형태 — 맛이 좋아 식사 후나 입이 심심할 때 간식처럼 먹기 좋음
+씹어 먹기 편한 식감 — 오독오독 씹어 먹기 좋아서 섭취가 간편함
+가벼운 몸 상태 체감 — 섭취 후 몸이 한결 가벼워지는 느낌을 받음</t>
+        </is>
+      </c>
+      <c r="K8" s="3" t="inlineStr">
+        <is>
+          <t>복통 없는 확실한 배변 — 배가 아프거나 불편함 없이 화장실을 잘 가도록 도와줌
+위생적인 개별 스틱 포장 — 한 포씩 개별 포장되어 챙겨 먹기 편함
+부담 없는 저렴한 가격 — 가격이 저렴하여 자주 구매하기 좋음</t>
+        </is>
+      </c>
+      <c r="L8" s="3" t="inlineStr">
+        <is>
+          <t>뛰어난 가성비 — 가격 부담이 적어 지속 구매하기에 가성비가 훌륭함
+체중 유지 도움 — 더 이상 체중이 증가하지 않도록 유지하는 데 도움 됨</t>
+        </is>
+      </c>
+    </row>
+    <row r="9" ht="60" customHeight="1">
       <c r="B9" s="1" t="inlineStr">
         <is>
           <t>부정리뷰</t>
         </is>
       </c>
-      <c r="C9" s="3" t="inlineStr"/>
+      <c r="C9" s="3" t="inlineStr">
+        <is>
+          <t>섭취 후 피로감 유발 — 먹고 나면 잠이 오고 피곤한 느낌이 듦
+체감 효과의 부족 — 다이어트 체중 감량 효과가 크게 느껴지지 않음</t>
+        </is>
+      </c>
       <c r="D9" s="3" t="inlineStr"/>
       <c r="E9" s="3" t="inlineStr"/>
-      <c r="F9" s="3" t="inlineStr"/>
-      <c r="G9" s="3" t="inlineStr"/>
-      <c r="H9" s="3" t="inlineStr"/>
+      <c r="F9" s="3" t="inlineStr">
+        <is>
+          <t>미미한 효과 체감 — 체감되는 효과가 뚜렷하지는 않음</t>
+        </is>
+      </c>
+      <c r="G9" s="3" t="inlineStr">
+        <is>
+          <t>아쉬운 제품 끝맛 — 첫맛은 매우 맛있으나 끝맛이 살짝 아쉬움</t>
+        </is>
+      </c>
+      <c r="H9" s="3" t="inlineStr">
+        <is>
+          <t>뚜렷한 효과 미체감 — 꾸준히 먹고 있으나 즉각적인 효과 체감은 명확하지 않음</t>
+        </is>
+      </c>
       <c r="I9" s="3" t="inlineStr"/>
-      <c r="J9" s="3" t="inlineStr"/>
+      <c r="J9" s="3" t="inlineStr">
+        <is>
+          <t>이상한 맛과 식감 — 맛이 없고 씹을 때 질감이나 식감이 거부감을 줄 수 있음</t>
+        </is>
+      </c>
       <c r="K9" s="3" t="inlineStr"/>
-      <c r="L9" s="3" t="inlineStr"/>
+      <c r="L9" s="3" t="inlineStr">
+        <is>
+          <t>체중 감량 효과 미흡 — 약 복용만으로는 직접적인 체중 감량 효과가 크지 않음</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="B10" s="1" t="inlineStr">
@@ -5452,42 +6135,42 @@
       </c>
       <c r="D10" s="3" t="inlineStr">
         <is>
+          <t>1,000원</t>
+        </is>
+      </c>
+      <c r="E10" s="3" t="inlineStr">
+        <is>
           <t>5,000원</t>
         </is>
       </c>
-      <c r="E10" s="3" t="inlineStr">
+      <c r="F10" s="3" t="inlineStr">
         <is>
           <t>5,000원</t>
         </is>
       </c>
-      <c r="F10" s="3" t="inlineStr">
+      <c r="G10" s="3" t="inlineStr">
+        <is>
+          <t>5,000원</t>
+        </is>
+      </c>
+      <c r="H10" s="3" t="inlineStr">
+        <is>
+          <t>5,000원</t>
+        </is>
+      </c>
+      <c r="I10" s="3" t="inlineStr">
         <is>
           <t>2,000원</t>
         </is>
       </c>
-      <c r="G10" s="3" t="inlineStr">
+      <c r="J10" s="3" t="inlineStr">
+        <is>
+          <t>3,000원</t>
+        </is>
+      </c>
+      <c r="K10" s="3" t="inlineStr">
         <is>
           <t>5,000원</t>
-        </is>
-      </c>
-      <c r="H10" s="3" t="inlineStr">
-        <is>
-          <t>3,000원</t>
-        </is>
-      </c>
-      <c r="I10" s="3" t="inlineStr">
-        <is>
-          <t>1,000원</t>
-        </is>
-      </c>
-      <c r="J10" s="3" t="inlineStr">
-        <is>
-          <t>5,000원</t>
-        </is>
-      </c>
-      <c r="K10" s="3" t="inlineStr">
-        <is>
-          <t>1,000원</t>
         </is>
       </c>
       <c r="L10" s="3" t="inlineStr">
@@ -5714,7 +6397,7 @@
     <row r="3" ht="38" customHeight="1">
       <c r="B3" t="inlineStr">
         <is>
-          <t>피부/미용</t>
+          <t>프로바이오틱스/유산균</t>
         </is>
       </c>
       <c r="C3" t="n">
@@ -5722,27 +6405,27 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>[피부건강] 글로우뮤즈 스킨 밸런스 파우더 레몬맛 14포 (14일분)</t>
+          <t>지노마스터 질유산균 30캡슐 기획 (+보라지유 5일분) (1개월분)</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>글로우뮤즈</t>
+          <t>지노마스터</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>26,800원</t>
+          <t>27,400원</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>https://www.oliveyoung.co.kr/store/goods/getGoodsDetail.do?goodsNo=A000000246272&amp;dispCatNo=90000010009&amp;trackingCd=Best_Sellingbest&amp;t_page=%EB%9E%AD%ED%82%B9&amp;t_click=%ED%8C%90%EB%A7%A4%EB%9E%AD%ED%82%B9_%EA%B1%B4%EA%B0%95%EC%8B%9D%ED%92%88_%EC%83%81%ED%92%88%EC%83%81%EC%84%B8&amp;t_number=2</t>
+          <t>https://www.oliveyoung.co.kr/store/goods/getGoodsDetail.do?goodsNo=A000000244929&amp;dispCatNo=90000010009&amp;trackingCd=Best_Sellingbest&amp;t_page=%EB%9E%AD%ED%82%B9&amp;t_click=%ED%8C%90%EB%A7%A4%EB%9E%AD%ED%82%B9_%EA%B1%B4%EA%B0%95%EC%8B%9D%ED%92%88_%EC%83%81%ED%92%88%EC%83%81%EC%84%B8&amp;t_number=2</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>https://image.oliveyoung.co.kr/cfimages/cf-goods/uploads/images/thumbnails/400/10/0000/0024/A00000024627206ko.jpg?l=ko</t>
+          <t>https://image.oliveyoung.co.kr/cfimages/cf-goods/uploads/images/thumbnails/400/10/0000/0024/A00000024492948ko.jpg?l=ko</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -5757,7 +6440,7 @@
     <row r="4" ht="38" customHeight="1">
       <c r="B4" t="inlineStr">
         <is>
-          <t>피부/미용</t>
+          <t>다이어트/체중관리</t>
         </is>
       </c>
       <c r="C4" t="n">
@@ -5765,27 +6448,27 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>[10/18 하루특가] 비비랩 화이트 콜라겐 18+2/30포 (20일/30일분)</t>
+          <t>[한선화 PICK] 프로뉴트리션 듀얼플랜 다이어트 유산균 14포</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>비비랩</t>
+          <t>프로뉴트리션</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>11,400원</t>
+          <t>35,800원</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>https://www.oliveyoung.co.kr/store/goods/getGoodsDetail.do?goodsNo=A000000248072&amp;dispCatNo=90000010009&amp;trackingCd=Best_Sellingbest&amp;t_page=%EB%9E%AD%ED%82%B9&amp;t_click=%ED%8C%90%EB%A7%A4%EB%9E%AD%ED%82%B9_%EA%B1%B4%EA%B0%95%EC%8B%9D%ED%92%88_%EC%83%81%ED%92%88%EC%83%81%EC%84%B8&amp;t_number=3</t>
+          <t>https://www.oliveyoung.co.kr/store/goods/getGoodsDetail.do?goodsNo=A000000205496&amp;dispCatNo=90000010009&amp;trackingCd=Best_Sellingbest&amp;t_page=%EB%9E%AD%ED%82%B9&amp;t_click=%ED%8C%90%EB%A7%A4%EB%9E%AD%ED%82%B9_%EA%B1%B4%EA%B0%95%EC%8B%9D%ED%92%88_%EC%83%81%ED%92%88%EC%83%81%EC%84%B8&amp;t_number=3</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>https://image.oliveyoung.co.kr/cfimages/cf-goods/uploads/images/thumbnails/400/10/0000/0024/A00000024807247ko.png?l=ko</t>
+          <t>https://image.oliveyoung.co.kr/cfimages/cf-goods/uploads/images/thumbnails/400/10/0000/0020/A00000020549621ko.jpg?l=ko</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -5800,7 +6483,7 @@
     <row r="5" ht="38" customHeight="1">
       <c r="B5" t="inlineStr">
         <is>
-          <t>프로바이오틱스/유산균</t>
+          <t>피부/미용</t>
         </is>
       </c>
       <c r="C5" t="n">
@@ -5808,27 +6491,27 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>지노마스터 질유산균 30캡슐 기획 (+보라지유 5일분) (1개월분)</t>
+          <t>[피부건강] 글로우뮤즈 스킨 밸런스 파우더 레몬맛 14포 (14일분)</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>지노마스터</t>
+          <t>글로우뮤즈</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>27,400원</t>
+          <t>26,800원</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>https://www.oliveyoung.co.kr/store/goods/getGoodsDetail.do?goodsNo=A000000244929&amp;dispCatNo=90000010009&amp;trackingCd=Best_Sellingbest&amp;t_page=%EB%9E%AD%ED%82%B9&amp;t_click=%ED%8C%90%EB%A7%A4%EB%9E%AD%ED%82%B9_%EA%B1%B4%EA%B0%95%EC%8B%9D%ED%92%88_%EC%83%81%ED%92%88%EC%83%81%EC%84%B8&amp;t_number=4</t>
+          <t>https://www.oliveyoung.co.kr/store/goods/getGoodsDetail.do?goodsNo=A000000246272&amp;dispCatNo=90000010009&amp;trackingCd=Best_Sellingbest&amp;t_page=%EB%9E%AD%ED%82%B9&amp;t_click=%ED%8C%90%EB%A7%A4%EB%9E%AD%ED%82%B9_%EA%B1%B4%EA%B0%95%EC%8B%9D%ED%92%88_%EC%83%81%ED%92%88%EC%83%81%EC%84%B8&amp;t_number=4</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>https://image.oliveyoung.co.kr/cfimages/cf-goods/uploads/images/thumbnails/400/10/0000/0024/A00000024492948ko.jpg?l=ko</t>
+          <t>https://image.oliveyoung.co.kr/cfimages/cf-goods/uploads/images/thumbnails/400/10/0000/0024/A00000024627206ko.jpg?l=ko</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -5843,7 +6526,7 @@
     <row r="6" ht="38" customHeight="1">
       <c r="B6" t="inlineStr">
         <is>
-          <t>프로바이오틱스/유산균</t>
+          <t>비타민C/항산화</t>
         </is>
       </c>
       <c r="C6" t="n">
@@ -5851,34 +6534,46 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>[덴프스] 덴마크 유산균이야기 30캡슐 1+1 기획 (+트루바이타민 3포 증정)</t>
+          <t>고려은단 비타민C1000 120정 (4개월분)</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>덴프스</t>
+          <t>고려은단</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>30,400원</t>
+          <t>12,900원</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>https://www.oliveyoung.co.kr/store/goods/getGoodsDetail.do?goodsNo=A000000206861&amp;dispCatNo=90000010009&amp;trackingCd=Best_Sellingbest&amp;t_page=%EB%9E%AD%ED%82%B9&amp;t_click=%ED%8C%90%EB%A7%A4%EB%9E%AD%ED%82%B9_%EA%B1%B4%EA%B0%95%EC%8B%9D%ED%92%88_%EC%83%81%ED%92%88%EC%83%81%EC%84%B8&amp;t_number=5</t>
+          <t>https://www.oliveyoung.co.kr/store/goods/getGoodsDetail.do?goodsNo=A000000002944&amp;dispCatNo=90000010009&amp;trackingCd=Best_Sellingbest&amp;t_page=%EB%9E%AD%ED%82%B9&amp;t_click=%ED%8C%90%EB%A7%A4%EB%9E%AD%ED%82%B9_%EA%B1%B4%EA%B0%95%EC%8B%9D%ED%92%88_%EC%83%81%ED%92%88%EC%83%81%EC%84%B8&amp;t_number=5</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>https://image.oliveyoung.co.kr/cfimages/cf-goods/uploads/images/thumbnails/400/10/0000/0020/A00000020686148ko.jpg?l=ko</t>
+          <t>https://image.oliveyoung.co.kr/cfimages/cf-goods/uploads/images/thumbnails/400/10/0000/0000/A00000000294414ko.jpg?l=ko</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
       <c r="J6" t="inlineStr"/>
-      <c r="K6" t="inlineStr"/>
-      <c r="L6" t="inlineStr"/>
-      <c r="M6" t="inlineStr"/>
+      <c r="K6" t="inlineStr">
+        <is>
+          <t>높은 브랜드 신뢰도 — 대한민국 1등 비타민 브랜드로 신뢰하고 먹음</t>
+        </is>
+      </c>
+      <c r="L6" t="inlineStr">
+        <is>
+          <t>피로 완화 및 컨디션 관리 — 매일 섭취 시 피로감을 줄이고 컨디션을 올리는 데 도움 됨</t>
+        </is>
+      </c>
+      <c r="M6" t="inlineStr">
+        <is>
+          <t>데일리 필수 영양제 — 현대인에게 꼭 필요한 영양제로 꾸준히 챙겨 먹기 좋음</t>
+        </is>
+      </c>
       <c r="N6" t="inlineStr"/>
       <c r="O6" t="inlineStr"/>
       <c r="P6" t="inlineStr"/>
@@ -5886,7 +6581,7 @@
     <row r="7" ht="38" customHeight="1">
       <c r="B7" t="inlineStr">
         <is>
-          <t>프로바이오틱스/유산균</t>
+          <t>기타/특수목적</t>
         </is>
       </c>
       <c r="C7" t="n">
@@ -5894,31 +6589,35 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>CJ BYOCORE 바나나효소 30포 + 키캡 키링 (1개월분)</t>
+          <t>[곽민경 PICK] 생활약속 기분전환 알파플러스 10포 (+1포 증정기획)</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>바이오코어유산균</t>
+          <t>생활약속</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>24,000원</t>
+          <t>16,200원</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>https://www.oliveyoung.co.kr/store/goods/getGoodsDetail.do?goodsNo=A000000261662&amp;dispCatNo=90000010009&amp;trackingCd=Best_Sellingbest&amp;t_page=%EB%9E%AD%ED%82%B9&amp;t_click=%ED%8C%90%EB%A7%A4%EB%9E%AD%ED%82%B9_%EA%B1%B4%EA%B0%95%EC%8B%9D%ED%92%88_%EC%83%81%ED%92%88%EC%83%81%EC%84%B8&amp;t_number=6</t>
+          <t>https://www.oliveyoung.co.kr/store/goods/getGoodsDetail.do?goodsNo=A000000180121&amp;dispCatNo=90000010009&amp;trackingCd=Best_Sellingbest&amp;t_page=%EB%9E%AD%ED%82%B9&amp;t_click=%ED%8C%90%EB%A7%A4%EB%9E%AD%ED%82%B9_%EA%B1%B4%EA%B0%95%EC%8B%9D%ED%92%88_%EC%83%81%ED%92%88%EC%83%81%EC%84%B8&amp;t_number=6</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>https://image.oliveyoung.co.kr/cfimages/cf-goods/uploads/images/thumbnails/400/10/0000/0026/A00000026166204ko.jpg?l=ko</t>
-        </is>
-      </c>
-      <c r="I7" t="inlineStr"/>
-      <c r="J7" t="inlineStr"/>
+          <t>https://image.oliveyoung.co.kr/cfimages/cf-goods/uploads/images/thumbnails/400/10/0000/0018/A00000018012128ko.jpg?l=ko</t>
+        </is>
+      </c>
+      <c r="I7" t="n">
+        <v>4.8</v>
+      </c>
+      <c r="J7" t="n">
+        <v>17509</v>
+      </c>
       <c r="K7" t="inlineStr"/>
       <c r="L7" t="inlineStr"/>
       <c r="M7" t="inlineStr"/>
@@ -5929,7 +6628,7 @@
     <row r="8" ht="38" customHeight="1">
       <c r="B8" t="inlineStr">
         <is>
-          <t>멀티비타민/종합비타민</t>
+          <t>기타/특수목적</t>
         </is>
       </c>
       <c r="C8" t="n">
@@ -5937,27 +6636,27 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>오쏘몰 이뮨 멀티비타민&amp;미네랄 14+1입</t>
+          <t>[올영단독] 칼로 스탑 PLUS 15포 + 컨트롤 PLUS 15포 기획 (1개월분)</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>오쏘몰</t>
+          <t>칼로(Kalo)</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>61,900원</t>
+          <t>19,900원</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>https://www.oliveyoung.co.kr/store/goods/getGoodsDetail.do?goodsNo=A000000193086&amp;dispCatNo=90000010009&amp;trackingCd=Best_Sellingbest&amp;t_page=%EB%9E%AD%ED%82%B9&amp;t_click=%ED%8C%90%EB%A7%A4%EB%9E%AD%ED%82%B9_%EA%B1%B4%EA%B0%95%EC%8B%9D%ED%92%88_%EC%83%81%ED%92%88%EC%83%81%EC%84%B8&amp;t_number=7</t>
+          <t>https://www.oliveyoung.co.kr/store/goods/getGoodsDetail.do?goodsNo=A000000176758&amp;dispCatNo=90000010009&amp;trackingCd=Best_Sellingbest&amp;t_page=%EB%9E%AD%ED%82%B9&amp;t_click=%ED%8C%90%EB%A7%A4%EB%9E%AD%ED%82%B9_%EA%B1%B4%EA%B0%95%EC%8B%9D%ED%92%88_%EC%83%81%ED%92%88%EC%83%81%EC%84%B8&amp;t_number=7</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>https://image.oliveyoung.co.kr/cfimages/cf-goods/uploads/images/thumbnails/400/10/0000/0019/A00000019308652ko.jpg?l=ko</t>
+          <t>https://image.oliveyoung.co.kr/cfimages/cf-goods/uploads/images/thumbnails/400/10/0000/0017/A00000017675815ko.png?l=ko</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -5972,7 +6671,7 @@
     <row r="9" ht="38" customHeight="1">
       <c r="B9" t="inlineStr">
         <is>
-          <t>기타/특수목적</t>
+          <t>프로바이오틱스/유산균</t>
         </is>
       </c>
       <c r="C9" t="n">
@@ -5980,27 +6679,27 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>[골라담기] CJ웰케어 건강루틴 가격혁명 12종 택 1</t>
+          <t>[덴프스] 덴마크 유산균이야기 30캡슐 1+1 기획 (+트루바이타민 3포 증정)</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>씨제이웰케어</t>
+          <t>덴프스</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>5,900원</t>
+          <t>30,400원</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>https://www.oliveyoung.co.kr/store/goods/getGoodsDetail.do?goodsNo=A000000247861&amp;dispCatNo=90000010009&amp;trackingCd=Best_Sellingbest&amp;t_page=%EB%9E%AD%ED%82%B9&amp;t_click=%ED%8C%90%EB%A7%A4%EB%9E%AD%ED%82%B9_%EA%B1%B4%EA%B0%95%EC%8B%9D%ED%92%88_%EC%83%81%ED%92%88%EC%83%81%EC%84%B8&amp;t_number=8</t>
+          <t>https://www.oliveyoung.co.kr/store/goods/getGoodsDetail.do?goodsNo=A000000206861&amp;dispCatNo=90000010009&amp;trackingCd=Best_Sellingbest&amp;t_page=%EB%9E%AD%ED%82%B9&amp;t_click=%ED%8C%90%EB%A7%A4%EB%9E%AD%ED%82%B9_%EA%B1%B4%EA%B0%95%EC%8B%9D%ED%92%88_%EC%83%81%ED%92%88%EC%83%81%EC%84%B8&amp;t_number=8</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>https://image.oliveyoung.co.kr/cfimages/cf-goods/uploads/images/thumbnails/400/10/0000/0024/A00000024786106ko.jpg?l=ko</t>
+          <t>https://image.oliveyoung.co.kr/cfimages/cf-goods/uploads/images/thumbnails/400/10/0000/0020/A00000020686148ko.jpg?l=ko</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -6046,11 +6745,27 @@
           <t>https://image.oliveyoung.co.kr/cfimages/cf-goods/uploads/images/thumbnails/400/10/0000/0023/A00000023821422ko.png?l=ko</t>
         </is>
       </c>
-      <c r="I10" t="inlineStr"/>
-      <c r="J10" t="inlineStr"/>
-      <c r="K10" t="inlineStr"/>
-      <c r="L10" t="inlineStr"/>
-      <c r="M10" t="inlineStr"/>
+      <c r="I10" t="n">
+        <v>4.8</v>
+      </c>
+      <c r="J10" t="n">
+        <v>974</v>
+      </c>
+      <c r="K10" t="inlineStr">
+        <is>
+          <t>피부 건조 및 탄력 케어 — 피부 보습과 탄력 저하 등 근본적인 피부 케어에 도움 됨</t>
+        </is>
+      </c>
+      <c r="L10" t="inlineStr">
+        <is>
+          <t>우수한 맛과 섭취감 — 맛이 매우 뛰어나 거부감 없이 쉽게 섭취 가능함</t>
+        </is>
+      </c>
+      <c r="M10" t="inlineStr">
+        <is>
+          <t>식약처 인증 기능성 — 피부 2중 기능성 인증으로 믿고 주변에 추천할 수 있음</t>
+        </is>
+      </c>
       <c r="N10" t="inlineStr"/>
       <c r="O10" t="inlineStr"/>
       <c r="P10" t="inlineStr"/>
@@ -6058,7 +6773,7 @@
     <row r="11" ht="38" customHeight="1">
       <c r="B11" t="inlineStr">
         <is>
-          <t>기타/특수목적</t>
+          <t>피부/미용</t>
         </is>
       </c>
       <c r="C11" t="n">
@@ -6066,38 +6781,50 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>grn+ 분홍이(105정)+초록이(70정) 기획세트 (35일분)</t>
+          <t>[10/18 하루특가] 비비랩 화이트 콜라겐 18+2/30포 (20일/30일분)</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>grn+</t>
+          <t>비비랩</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>27,900원</t>
+          <t>11,400원</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>https://www.oliveyoung.co.kr/store/goods/getGoodsDetail.do?goodsNo=A000000186058&amp;dispCatNo=90000010009&amp;trackingCd=Best_Sellingbest&amp;t_page=%EB%9E%AD%ED%82%B9&amp;t_click=%ED%8C%90%EB%A7%A4%EB%9E%AD%ED%82%B9_%EA%B1%B4%EA%B0%95%EC%8B%9D%ED%92%88_%EC%83%81%ED%92%88%EC%83%81%EC%84%B8&amp;t_number=10</t>
+          <t>https://www.oliveyoung.co.kr/store/goods/getGoodsDetail.do?goodsNo=A000000248072&amp;dispCatNo=90000010009&amp;trackingCd=Best_Sellingbest&amp;t_page=%EB%9E%AD%ED%82%B9&amp;t_click=%ED%8C%90%EB%A7%A4%EB%9E%AD%ED%82%B9_%EA%B1%B4%EA%B0%95%EC%8B%9D%ED%92%88_%EC%83%81%ED%92%88%EC%83%81%EC%84%B8&amp;t_number=10</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>https://image.oliveyoung.co.kr/cfimages/cf-goods/uploads/images/thumbnails/400/10/0000/0018/A00000018605851ko.jpg?l=ko</t>
+          <t>https://image.oliveyoung.co.kr/cfimages/cf-goods/uploads/images/thumbnails/400/10/0000/0024/A00000024807247ko.png?l=ko</t>
         </is>
       </c>
       <c r="I11" t="n">
-        <v>4.7</v>
+        <v>4.9</v>
       </c>
       <c r="J11" t="n">
-        <v>6680</v>
-      </c>
-      <c r="K11" t="inlineStr"/>
-      <c r="L11" t="inlineStr"/>
-      <c r="M11" t="inlineStr"/>
+        <v>2713</v>
+      </c>
+      <c r="K11" t="inlineStr">
+        <is>
+          <t>맛있는 복숭아 맛 — 자두사탕 느낌의 달콤한 복숭아 맛으로 섭취가 즐거움</t>
+        </is>
+      </c>
+      <c r="L11" t="inlineStr">
+        <is>
+          <t>강력한 저분자 콜라겐 함량 — 기존 대비 2배 강력해진 저분자 콜라겐 2,400mg을 포함함</t>
+        </is>
+      </c>
+      <c r="M11" t="inlineStr">
+        <is>
+          <t>속부터 밝히는 피부 케어 — 속부터 화사하게 케어하며 메이크업 전 피부 푸석함 완화에 도움 됨</t>
+        </is>
+      </c>
       <c r="N11" t="inlineStr"/>
       <c r="O11" t="inlineStr"/>
       <c r="P11" t="inlineStr"/>
@@ -6218,47 +6945,47 @@
       </c>
       <c r="D3" s="3" t="inlineStr">
         <is>
+          <t>프로바이오틱스/유산균</t>
+        </is>
+      </c>
+      <c r="E3" s="3" t="inlineStr">
+        <is>
+          <t>다이어트/체중관리</t>
+        </is>
+      </c>
+      <c r="F3" s="3" t="inlineStr">
+        <is>
           <t>피부/미용</t>
         </is>
       </c>
-      <c r="E3" s="3" t="inlineStr">
+      <c r="G3" s="3" t="inlineStr">
+        <is>
+          <t>비타민C/항산화</t>
+        </is>
+      </c>
+      <c r="H3" s="3" t="inlineStr">
+        <is>
+          <t>기타/특수목적</t>
+        </is>
+      </c>
+      <c r="I3" s="3" t="inlineStr">
+        <is>
+          <t>기타/특수목적</t>
+        </is>
+      </c>
+      <c r="J3" s="3" t="inlineStr">
+        <is>
+          <t>프로바이오틱스/유산균</t>
+        </is>
+      </c>
+      <c r="K3" s="3" t="inlineStr">
         <is>
           <t>피부/미용</t>
         </is>
       </c>
-      <c r="F3" s="3" t="inlineStr">
-        <is>
-          <t>프로바이오틱스/유산균</t>
-        </is>
-      </c>
-      <c r="G3" s="3" t="inlineStr">
-        <is>
-          <t>프로바이오틱스/유산균</t>
-        </is>
-      </c>
-      <c r="H3" s="3" t="inlineStr">
-        <is>
-          <t>프로바이오틱스/유산균</t>
-        </is>
-      </c>
-      <c r="I3" s="3" t="inlineStr">
-        <is>
-          <t>멀티비타민/종합비타민</t>
-        </is>
-      </c>
-      <c r="J3" s="3" t="inlineStr">
-        <is>
-          <t>기타/특수목적</t>
-        </is>
-      </c>
-      <c r="K3" s="3" t="inlineStr">
+      <c r="L3" s="3" t="inlineStr">
         <is>
           <t>피부/미용</t>
-        </is>
-      </c>
-      <c r="L3" s="3" t="inlineStr">
-        <is>
-          <t>기타/특수목적</t>
         </is>
       </c>
     </row>
@@ -6275,47 +7002,47 @@
       </c>
       <c r="D4" s="3" t="inlineStr">
         <is>
+          <t>지노마스터</t>
+        </is>
+      </c>
+      <c r="E4" s="3" t="inlineStr">
+        <is>
+          <t>프로뉴트리션</t>
+        </is>
+      </c>
+      <c r="F4" s="3" t="inlineStr">
+        <is>
           <t>글로우뮤즈</t>
         </is>
       </c>
-      <c r="E4" s="3" t="inlineStr">
+      <c r="G4" s="3" t="inlineStr">
+        <is>
+          <t>고려은단</t>
+        </is>
+      </c>
+      <c r="H4" s="3" t="inlineStr">
+        <is>
+          <t>생활약속</t>
+        </is>
+      </c>
+      <c r="I4" s="3" t="inlineStr">
+        <is>
+          <t>칼로(Kalo)</t>
+        </is>
+      </c>
+      <c r="J4" s="3" t="inlineStr">
+        <is>
+          <t>덴프스</t>
+        </is>
+      </c>
+      <c r="K4" s="3" t="inlineStr">
+        <is>
+          <t>에버콜라겐</t>
+        </is>
+      </c>
+      <c r="L4" s="3" t="inlineStr">
         <is>
           <t>비비랩</t>
-        </is>
-      </c>
-      <c r="F4" s="3" t="inlineStr">
-        <is>
-          <t>지노마스터</t>
-        </is>
-      </c>
-      <c r="G4" s="3" t="inlineStr">
-        <is>
-          <t>덴프스</t>
-        </is>
-      </c>
-      <c r="H4" s="3" t="inlineStr">
-        <is>
-          <t>바이오코어유산균</t>
-        </is>
-      </c>
-      <c r="I4" s="3" t="inlineStr">
-        <is>
-          <t>오쏘몰</t>
-        </is>
-      </c>
-      <c r="J4" s="3" t="inlineStr">
-        <is>
-          <t>씨제이웰케어</t>
-        </is>
-      </c>
-      <c r="K4" s="3" t="inlineStr">
-        <is>
-          <t>에버콜라겐</t>
-        </is>
-      </c>
-      <c r="L4" s="3" t="inlineStr">
-        <is>
-          <t>grn+</t>
         </is>
       </c>
     </row>
@@ -6332,47 +7059,47 @@
       </c>
       <c r="D5" s="3" t="inlineStr">
         <is>
+          <t>지노마스터 질유산균 30캡슐 기획 (+보라지유 5일분) (1개월분)</t>
+        </is>
+      </c>
+      <c r="E5" s="3" t="inlineStr">
+        <is>
+          <t>[한선화 PICK] 프로뉴트리션 듀얼플랜 다이어트 유산균 14포</t>
+        </is>
+      </c>
+      <c r="F5" s="3" t="inlineStr">
+        <is>
           <t>[피부건강] 글로우뮤즈 스킨 밸런스 파우더 레몬맛 14포 (14일분)</t>
         </is>
       </c>
-      <c r="E5" s="3" t="inlineStr">
+      <c r="G5" s="3" t="inlineStr">
+        <is>
+          <t>고려은단 비타민C1000 120정 (4개월분)</t>
+        </is>
+      </c>
+      <c r="H5" s="3" t="inlineStr">
+        <is>
+          <t>[곽민경 PICK] 생활약속 기분전환 알파플러스 10포 (+1포 증정기획)</t>
+        </is>
+      </c>
+      <c r="I5" s="3" t="inlineStr">
+        <is>
+          <t>[올영단독] 칼로 스탑 PLUS 15포 + 컨트롤 PLUS 15포 기획 (1개월분)</t>
+        </is>
+      </c>
+      <c r="J5" s="3" t="inlineStr">
+        <is>
+          <t>[덴프스] 덴마크 유산균이야기 30캡슐 1+1 기획 (+트루바이타민 3포 증정)</t>
+        </is>
+      </c>
+      <c r="K5" s="3" t="inlineStr">
+        <is>
+          <t>[OY단독] 에버콜라겐 타임 비오틴 셀 30포 (+3포 증정기획)</t>
+        </is>
+      </c>
+      <c r="L5" s="3" t="inlineStr">
         <is>
           <t>[10/18 하루특가] 비비랩 화이트 콜라겐 18+2/30포 (20일/30일분)</t>
-        </is>
-      </c>
-      <c r="F5" s="3" t="inlineStr">
-        <is>
-          <t>지노마스터 질유산균 30캡슐 기획 (+보라지유 5일분) (1개월분)</t>
-        </is>
-      </c>
-      <c r="G5" s="3" t="inlineStr">
-        <is>
-          <t>[덴프스] 덴마크 유산균이야기 30캡슐 1+1 기획 (+트루바이타민 3포 증정)</t>
-        </is>
-      </c>
-      <c r="H5" s="3" t="inlineStr">
-        <is>
-          <t>CJ BYOCORE 바나나효소 30포 + 키캡 키링 (1개월분)</t>
-        </is>
-      </c>
-      <c r="I5" s="3" t="inlineStr">
-        <is>
-          <t>오쏘몰 이뮨 멀티비타민&amp;미네랄 14+1입</t>
-        </is>
-      </c>
-      <c r="J5" s="3" t="inlineStr">
-        <is>
-          <t>[골라담기] CJ웰케어 건강루틴 가격혁명 12종 택 1</t>
-        </is>
-      </c>
-      <c r="K5" s="3" t="inlineStr">
-        <is>
-          <t>[OY단독] 에버콜라겐 타임 비오틴 셀 30포 (+3포 증정기획)</t>
-        </is>
-      </c>
-      <c r="L5" s="3" t="inlineStr">
-        <is>
-          <t>grn+ 분홍이(105정)+초록이(70정) 기획세트 (35일분)</t>
         </is>
       </c>
     </row>
@@ -6387,12 +7114,16 @@
       <c r="E6" s="3" t="inlineStr"/>
       <c r="F6" s="3" t="inlineStr"/>
       <c r="G6" s="3" t="inlineStr"/>
-      <c r="H6" s="3" t="inlineStr"/>
+      <c r="H6" s="3" t="n">
+        <v>4.8</v>
+      </c>
       <c r="I6" s="3" t="inlineStr"/>
       <c r="J6" s="3" t="inlineStr"/>
-      <c r="K6" s="3" t="inlineStr"/>
+      <c r="K6" s="3" t="n">
+        <v>4.8</v>
+      </c>
       <c r="L6" s="3" t="n">
-        <v>4.7</v>
+        <v>4.9</v>
       </c>
     </row>
     <row r="7">
@@ -6406,15 +7137,19 @@
       <c r="E7" s="3" t="inlineStr"/>
       <c r="F7" s="3" t="inlineStr"/>
       <c r="G7" s="3" t="inlineStr"/>
-      <c r="H7" s="3" t="inlineStr"/>
+      <c r="H7" s="3" t="n">
+        <v>17509</v>
+      </c>
       <c r="I7" s="3" t="inlineStr"/>
       <c r="J7" s="3" t="inlineStr"/>
-      <c r="K7" s="3" t="inlineStr"/>
+      <c r="K7" s="3" t="n">
+        <v>974</v>
+      </c>
       <c r="L7" s="3" t="n">
-        <v>6680</v>
-      </c>
-    </row>
-    <row r="8">
+        <v>2713</v>
+      </c>
+    </row>
+    <row r="8" ht="90" customHeight="1">
       <c r="B8" s="1" t="inlineStr">
         <is>
           <t>긍정리뷰</t>
@@ -6424,12 +7159,30 @@
       <c r="D8" s="3" t="inlineStr"/>
       <c r="E8" s="3" t="inlineStr"/>
       <c r="F8" s="3" t="inlineStr"/>
-      <c r="G8" s="3" t="inlineStr"/>
+      <c r="G8" s="3" t="inlineStr">
+        <is>
+          <t>높은 브랜드 신뢰도 — 대한민국 1등 비타민 브랜드로 신뢰하고 먹음
+피로 완화 및 컨디션 관리 — 매일 섭취 시 피로감을 줄이고 컨디션을 올리는 데 도움 됨
+데일리 필수 영양제 — 현대인에게 꼭 필요한 영양제로 꾸준히 챙겨 먹기 좋음</t>
+        </is>
+      </c>
       <c r="H8" s="3" t="inlineStr"/>
       <c r="I8" s="3" t="inlineStr"/>
       <c r="J8" s="3" t="inlineStr"/>
-      <c r="K8" s="3" t="inlineStr"/>
-      <c r="L8" s="3" t="inlineStr"/>
+      <c r="K8" s="3" t="inlineStr">
+        <is>
+          <t>피부 건조 및 탄력 케어 — 피부 보습과 탄력 저하 등 근본적인 피부 케어에 도움 됨
+우수한 맛과 섭취감 — 맛이 매우 뛰어나 거부감 없이 쉽게 섭취 가능함
+식약처 인증 기능성 — 피부 2중 기능성 인증으로 믿고 주변에 추천할 수 있음</t>
+        </is>
+      </c>
+      <c r="L8" s="3" t="inlineStr">
+        <is>
+          <t>맛있는 복숭아 맛 — 자두사탕 느낌의 달콤한 복숭아 맛으로 섭취가 즐거움
+강력한 저분자 콜라겐 함량 — 기존 대비 2배 강력해진 저분자 콜라겐 2,400mg을 포함함
+속부터 밝히는 피부 케어 — 속부터 화사하게 케어하며 메이크업 전 피부 푸석함 완화에 도움 됨</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="B9" s="1" t="inlineStr">
@@ -6461,47 +7214,47 @@
       </c>
       <c r="D10" s="3" t="inlineStr">
         <is>
+          <t>27,400원</t>
+        </is>
+      </c>
+      <c r="E10" s="3" t="inlineStr">
+        <is>
+          <t>35,800원</t>
+        </is>
+      </c>
+      <c r="F10" s="3" t="inlineStr">
+        <is>
           <t>26,800원</t>
         </is>
       </c>
-      <c r="E10" s="3" t="inlineStr">
+      <c r="G10" s="3" t="inlineStr">
+        <is>
+          <t>12,900원</t>
+        </is>
+      </c>
+      <c r="H10" s="3" t="inlineStr">
+        <is>
+          <t>16,200원</t>
+        </is>
+      </c>
+      <c r="I10" s="3" t="inlineStr">
+        <is>
+          <t>19,900원</t>
+        </is>
+      </c>
+      <c r="J10" s="3" t="inlineStr">
+        <is>
+          <t>30,400원</t>
+        </is>
+      </c>
+      <c r="K10" s="3" t="inlineStr">
+        <is>
+          <t>23,000원</t>
+        </is>
+      </c>
+      <c r="L10" s="3" t="inlineStr">
         <is>
           <t>11,400원</t>
-        </is>
-      </c>
-      <c r="F10" s="3" t="inlineStr">
-        <is>
-          <t>27,400원</t>
-        </is>
-      </c>
-      <c r="G10" s="3" t="inlineStr">
-        <is>
-          <t>30,400원</t>
-        </is>
-      </c>
-      <c r="H10" s="3" t="inlineStr">
-        <is>
-          <t>24,000원</t>
-        </is>
-      </c>
-      <c r="I10" s="3" t="inlineStr">
-        <is>
-          <t>61,900원</t>
-        </is>
-      </c>
-      <c r="J10" s="3" t="inlineStr">
-        <is>
-          <t>5,900원</t>
-        </is>
-      </c>
-      <c r="K10" s="3" t="inlineStr">
-        <is>
-          <t>23,000원</t>
-        </is>
-      </c>
-      <c r="L10" s="3" t="inlineStr">
-        <is>
-          <t>27,900원</t>
         </is>
       </c>
     </row>
@@ -6631,16 +7384,16 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="C2" t="n">
-        <v>25</v>
+        <v>27.5</v>
       </c>
       <c r="D2" t="n">
         <v>4</v>
       </c>
       <c r="E2" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="F2" t="n">
         <v>2</v>
@@ -6653,10 +7406,10 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="C3" t="n">
-        <v>20</v>
+        <v>17.5</v>
       </c>
       <c r="D3" t="n">
         <v>7</v>
@@ -6665,7 +7418,7 @@
         <v>0</v>
       </c>
       <c r="F3" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="4">
@@ -6684,10 +7437,10 @@
         <v>5</v>
       </c>
       <c r="E4" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F4" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="5">
@@ -6697,10 +7450,10 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="C5" t="n">
-        <v>12.5</v>
+        <v>10</v>
       </c>
       <c r="D5" t="n">
         <v>1</v>
@@ -6709,7 +7462,7 @@
         <v>0</v>
       </c>
       <c r="F5" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
     </row>
     <row r="6">
@@ -6737,7 +7490,7 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>마그네슘</t>
+          <t>비타민C/항산화</t>
         </is>
       </c>
       <c r="B7" t="n">
@@ -6747,32 +7500,32 @@
         <v>5</v>
       </c>
       <c r="D7" t="n">
+        <v>1</v>
+      </c>
+      <c r="E7" t="n">
         <v>0</v>
       </c>
-      <c r="E7" t="n">
-        <v>2</v>
-      </c>
       <c r="F7" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>홍삼/인삼</t>
+          <t>비타민D</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C8" t="n">
-        <v>2.5</v>
+        <v>5</v>
       </c>
       <c r="D8" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E8" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="F8" t="n">
         <v>0</v>
@@ -6781,7 +7534,7 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>비타민C/항산화</t>
+          <t>혈행</t>
         </is>
       </c>
       <c r="B9" t="n">
@@ -6791,10 +7544,10 @@
         <v>2.5</v>
       </c>
       <c r="D9" t="n">
+        <v>0</v>
+      </c>
+      <c r="E9" t="n">
         <v>1</v>
-      </c>
-      <c r="E9" t="n">
-        <v>0</v>
       </c>
       <c r="F9" t="n">
         <v>0</v>
@@ -6825,7 +7578,7 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>비타민D</t>
+          <t>홍삼/인삼</t>
         </is>
       </c>
       <c r="B11" t="n">
@@ -6835,10 +7588,10 @@
         <v>2.5</v>
       </c>
       <c r="D11" t="n">
+        <v>1</v>
+      </c>
+      <c r="E11" t="n">
         <v>0</v>
-      </c>
-      <c r="E11" t="n">
-        <v>1</v>
       </c>
       <c r="F11" t="n">
         <v>0</v>
